--- a/ObvTarama_Gunluk_28082026_06:00.xlsx
+++ b/ObvTarama_Gunluk_28082026_06:00.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUMU" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KIRILIMLAR'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'YAKLASANLAR'!$A$1:$C$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUMU'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KIRILIMLAR'!$A$1:$CI$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'YAKLASANLAR'!$A$1:$CI$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUMU'!$A$1:$CI$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,14 @@
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006400"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="008B0000"/>
     </font>
   </fonts>
   <fills count="5">
@@ -83,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -92,7 +100,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,12 +470,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:CI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="7" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="27" max="27"/>
+    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="7" customWidth="1" min="29" max="29"/>
+    <col width="7" customWidth="1" min="30" max="30"/>
+    <col width="7" customWidth="1" min="31" max="31"/>
+    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="25" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="47" max="47"/>
+    <col width="19" customWidth="1" min="48" max="48"/>
+    <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="19" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="11" customWidth="1" min="53" max="53"/>
+    <col width="11" customWidth="1" min="54" max="54"/>
+    <col width="11" customWidth="1" min="55" max="55"/>
+    <col width="11" customWidth="1" min="56" max="56"/>
+    <col width="19" customWidth="1" min="57" max="57"/>
+    <col width="18" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="11" customWidth="1" min="60" max="60"/>
+    <col width="11" customWidth="1" min="61" max="61"/>
+    <col width="11" customWidth="1" min="62" max="62"/>
+    <col width="11" customWidth="1" min="63" max="63"/>
+    <col width="11" customWidth="1" min="64" max="64"/>
+    <col width="11" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="13" customWidth="1" min="69" max="69"/>
+    <col width="13" customWidth="1" min="70" max="70"/>
+    <col width="13" customWidth="1" min="71" max="71"/>
+    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="11" customWidth="1" min="80" max="80"/>
+    <col width="21" customWidth="1" min="81" max="81"/>
+    <col width="21" customWidth="1" min="82" max="82"/>
+    <col width="16" customWidth="1" min="83" max="83"/>
+    <col width="16" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="13" customWidth="1" min="86" max="86"/>
+    <col width="6" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,17 +570,2661 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Son fiyat</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük %</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Skor</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Hatta uzaklık %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>RSI 14</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>MACD hist</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Momentum %10</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ATR %</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>StochRSI K</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>StochRSI D</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>WT1</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>WT2</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>WT hist</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>SMI</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>SMI sinyal</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>E34</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>E55</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>5x8</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>8x13</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>13x21</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>21x34</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>34x55</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>E fan</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>VWAP fark %</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>Hacim oranı</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>Ort hacim</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>Baz hacim</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>Merdiven</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>Hacim onay</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>Özet</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 5x8</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 5x8</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 8x13</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 8x13</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 13x21</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 13x21</t>
+        </is>
+      </c>
+      <c r="AU1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 21x34</t>
+        </is>
+      </c>
+      <c r="AV1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 21x34</t>
+        </is>
+      </c>
+      <c r="AW1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 34x55</t>
+        </is>
+      </c>
+      <c r="AX1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 34x55</t>
+        </is>
+      </c>
+      <c r="AY1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E5</t>
+        </is>
+      </c>
+      <c r="AZ1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E8</t>
+        </is>
+      </c>
+      <c r="BA1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E13</t>
+        </is>
+      </c>
+      <c r="BB1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E21</t>
+        </is>
+      </c>
+      <c r="BC1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E34</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E55</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>▲ Yukarı kesenler</t>
+        </is>
+      </c>
+      <c r="BF1" s="2" t="inlineStr">
+        <is>
+          <t>▼ Aşağı kesenler</t>
+        </is>
+      </c>
+      <c r="BG1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük P</t>
+        </is>
+      </c>
+      <c r="BH1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R1</t>
+        </is>
+      </c>
+      <c r="BI1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R3</t>
+        </is>
+      </c>
+      <c r="BK1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S1</t>
+        </is>
+      </c>
+      <c r="BL1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S2</t>
+        </is>
+      </c>
+      <c r="BM1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S3</t>
+        </is>
+      </c>
+      <c r="BN1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık P</t>
+        </is>
+      </c>
+      <c r="BO1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R1</t>
+        </is>
+      </c>
+      <c r="BP1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R2</t>
+        </is>
+      </c>
+      <c r="BQ1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R3</t>
+        </is>
+      </c>
+      <c r="BR1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S1</t>
+        </is>
+      </c>
+      <c r="BS1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S2</t>
+        </is>
+      </c>
+      <c r="BT1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S3</t>
+        </is>
+      </c>
+      <c r="BU1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık P</t>
+        </is>
+      </c>
+      <c r="BV1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R1</t>
+        </is>
+      </c>
+      <c r="BW1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R2</t>
+        </is>
+      </c>
+      <c r="BX1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R3</t>
+        </is>
+      </c>
+      <c r="BY1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S1</t>
+        </is>
+      </c>
+      <c r="BZ1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S2</t>
+        </is>
+      </c>
+      <c r="CA1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S3</t>
+        </is>
+      </c>
+      <c r="CB1" s="2" t="inlineStr">
+        <is>
+          <t>Pivot ▲/▼</t>
+        </is>
+      </c>
+      <c r="CC1" s="2" t="inlineStr">
+        <is>
+          <t>Son pivot tepe</t>
+        </is>
+      </c>
+      <c r="CD1" s="2" t="inlineStr">
+        <is>
+          <t>Son pivot dip</t>
+        </is>
+      </c>
+      <c r="CE1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım tarihi</t>
+        </is>
+      </c>
+      <c r="CF1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım fiyatı</t>
+        </is>
+      </c>
+      <c r="CG1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım (gün önce)</t>
+        </is>
+      </c>
+      <c r="CH1" s="2" t="inlineStr">
+        <is>
+          <t>OBV kırılım</t>
+        </is>
+      </c>
+      <c r="CI1" s="2" t="inlineStr">
         <is>
           <t>Hata</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>AGESA</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>70.23</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>3.5711</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2.7738</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>7.6379</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>253.88</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>250.08</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>246.64</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>244.26</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>242.97</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>207.1883</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>264517</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>221633</v>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (15-06-26–06-08-26, ~%3.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 21-08-26 tarihinde önceden kırmıştı.</t>
+        </is>
+      </c>
+      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
+        </is>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25-08-26</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26-08-26</t>
+        </is>
+      </c>
+      <c r="AW2" s="3" t="inlineStr"/>
+      <c r="AX2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26-08-26</t>
+        </is>
+      </c>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr"/>
+      <c r="BC2" s="3" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr"/>
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="n">
+        <v>260.83</v>
+      </c>
+      <c r="BH2" s="3" t="n">
+        <v>264.67</v>
+      </c>
+      <c r="BI2" s="3" t="n">
+        <v>267.33</v>
+      </c>
+      <c r="BJ2" s="3" t="n">
+        <v>271.17</v>
+      </c>
+      <c r="BK2" s="3" t="n">
+        <v>258.17</v>
+      </c>
+      <c r="BL2" s="3" t="n">
+        <v>254.33</v>
+      </c>
+      <c r="BM2" s="3" t="n">
+        <v>251.67</v>
+      </c>
+      <c r="BN2" s="3" t="n">
+        <v>255.53</v>
+      </c>
+      <c r="BO2" s="3" t="n">
+        <v>269.97</v>
+      </c>
+      <c r="BP2" s="3" t="n">
+        <v>277.93</v>
+      </c>
+      <c r="BQ2" s="3" t="n">
+        <v>292.37</v>
+      </c>
+      <c r="BR2" s="3" t="n">
+        <v>247.57</v>
+      </c>
+      <c r="BS2" s="3" t="n">
+        <v>233.13</v>
+      </c>
+      <c r="BT2" s="3" t="n">
+        <v>225.17</v>
+      </c>
+      <c r="BU2" s="3" t="n">
+        <v>251.03</v>
+      </c>
+      <c r="BV2" s="3" t="n">
+        <v>274.47</v>
+      </c>
+      <c r="BW2" s="3" t="n">
+        <v>286.93</v>
+      </c>
+      <c r="BX2" s="3" t="n">
+        <v>310.37</v>
+      </c>
+      <c r="BY2" s="3" t="n">
+        <v>238.57</v>
+      </c>
+      <c r="BZ2" s="3" t="n">
+        <v>215.13</v>
+      </c>
+      <c r="CA2" s="3" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="CB2" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC2" s="3" t="inlineStr">
+        <is>
+          <t>T30 12-08-26 @246.1</t>
+        </is>
+      </c>
+      <c r="CD2" s="3" t="inlineStr">
+        <is>
+          <t>D29 18-08-26 @231.6</t>
+        </is>
+      </c>
+      <c r="CE2" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
+      <c r="CF2" s="3" t="n">
+        <v>251.75</v>
+      </c>
+      <c r="CG2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH2" s="3" t="inlineStr">
+        <is>
+          <t>21-08-26</t>
+        </is>
+      </c>
+      <c r="CI2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A1YEN</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>93.92</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y3" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Z3" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB3" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF3" s="5" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AG3" s="5" t="n">
+        <v>3.0427</v>
+      </c>
+      <c r="AH3" s="5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI3" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AJ3" s="5" t="n">
+        <v>23770802</v>
+      </c>
+      <c r="AK3" s="5" t="n">
+        <v>19927913</v>
+      </c>
+      <c r="AL3" s="5" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN3" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (13-05-26–10-08-26, ~%32.6 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 14-08-26 tarihinde önceden kırmıştı.</t>
+        </is>
+      </c>
+      <c r="AO3" s="5" t="inlineStr"/>
+      <c r="AP3" s="6" t="inlineStr">
+        <is>
+          <t>▲ 14-08-26</t>
+        </is>
+      </c>
+      <c r="AQ3" s="5" t="inlineStr"/>
+      <c r="AR3" s="6" t="inlineStr">
+        <is>
+          <t>▲ 18-08-26</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="inlineStr"/>
+      <c r="AT3" s="7" t="inlineStr">
+        <is>
+          <t>▼ 12-06-26</t>
+        </is>
+      </c>
+      <c r="AU3" s="5" t="inlineStr"/>
+      <c r="AV3" s="7" t="inlineStr">
+        <is>
+          <t>▼ 22-06-26</t>
+        </is>
+      </c>
+      <c r="AW3" s="5" t="inlineStr"/>
+      <c r="AX3" s="7" t="inlineStr">
+        <is>
+          <t>▼ 02-07-26</t>
+        </is>
+      </c>
+      <c r="AY3" s="5" t="inlineStr"/>
+      <c r="AZ3" s="5" t="inlineStr"/>
+      <c r="BA3" s="5" t="inlineStr"/>
+      <c r="BB3" s="5" t="inlineStr"/>
+      <c r="BC3" s="5" t="inlineStr"/>
+      <c r="BD3" s="5" t="inlineStr"/>
+      <c r="BE3" s="5" t="inlineStr"/>
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH3" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI3" s="5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BJ3" s="5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BK3" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BL3" s="5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BM3" s="5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN3" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BO3" s="5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP3" s="5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BQ3" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BR3" s="5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BS3" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BT3" s="5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BU3" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BV3" s="5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="BW3" s="5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BX3" s="5" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BY3" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BZ3" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CA3" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CB3" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC3" s="5" t="inlineStr">
+        <is>
+          <t>T29 25-08-26 @2.95</t>
+        </is>
+      </c>
+      <c r="CD3" s="5" t="inlineStr">
+        <is>
+          <t>D30 25-08-26 @2.72</t>
+        </is>
+      </c>
+      <c r="CE3" s="5" t="inlineStr">
+        <is>
+          <t>17-08-26</t>
+        </is>
+      </c>
+      <c r="CF3" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CG3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="CH3" s="5" t="inlineStr">
+        <is>
+          <t>14-08-26</t>
+        </is>
+      </c>
+      <c r="CI3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A1CAP</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.2832</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-36.54</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-287.49</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-363.06</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>11.1687</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>-22.64</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>6736736</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>7700768</v>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26-08-26</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 27-03-26</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-04-26</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="BS4" s="3" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="BT4" s="3" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BU4" s="3" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="BV4" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BW4" s="3" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="BX4" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BY4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ4" s="3" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="CA4" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC4" s="3" t="inlineStr">
+        <is>
+          <t>T26 18-08-26 @8.45</t>
+        </is>
+      </c>
+      <c r="CD4" s="3" t="inlineStr">
+        <is>
+          <t>D28 31-07-26 @8.58</t>
+        </is>
+      </c>
+      <c r="CE4" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
+      <c r="CF4" s="3" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="CG4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH4" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
+      <c r="CI4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ADEL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.7785</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>65.17</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>151.57</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>149.19</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="Y5" s="5" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="Z5" s="5" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF5" s="5" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="AG5" s="5" t="n">
+        <v>37.0379</v>
+      </c>
+      <c r="AH5" s="5" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="AI5" s="5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AJ5" s="5" t="n">
+        <v>10999396</v>
+      </c>
+      <c r="AK5" s="5" t="n">
+        <v>3843601</v>
+      </c>
+      <c r="AL5" s="5" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN5" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
+        </is>
+      </c>
+      <c r="AO5" s="5" t="inlineStr"/>
+      <c r="AP5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
+        </is>
+      </c>
+      <c r="AQ5" s="5" t="inlineStr"/>
+      <c r="AR5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
+        </is>
+      </c>
+      <c r="AS5" s="5" t="inlineStr"/>
+      <c r="AT5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 12-08-26</t>
+        </is>
+      </c>
+      <c r="AU5" s="5" t="inlineStr"/>
+      <c r="AV5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 20-08-26</t>
+        </is>
+      </c>
+      <c r="AW5" s="5" t="inlineStr"/>
+      <c r="AX5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 02-06-26</t>
+        </is>
+      </c>
+      <c r="AY5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ5" s="5" t="inlineStr"/>
+      <c r="BA5" s="5" t="inlineStr"/>
+      <c r="BB5" s="5" t="inlineStr"/>
+      <c r="BC5" s="5" t="inlineStr"/>
+      <c r="BD5" s="5" t="inlineStr"/>
+      <c r="BE5" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="BH5" s="5" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="BI5" s="5" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="BJ5" s="5" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="BK5" s="5" t="n">
+        <v>34.73</v>
+      </c>
+      <c r="BL5" s="5" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="BM5" s="5" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="BN5" s="5" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="BO5" s="5" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="BP5" s="5" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="BQ5" s="5" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="BR5" s="5" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="BS5" s="5" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="BT5" s="5" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="BU5" s="5" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="BV5" s="5" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="BW5" s="5" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="BX5" s="5" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="BY5" s="5" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="BZ5" s="5" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="CA5" s="5" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="CB5" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC5" s="5" t="inlineStr">
+        <is>
+          <t>T31 25-08-26 @39.1</t>
+        </is>
+      </c>
+      <c r="CD5" s="5" t="inlineStr">
+        <is>
+          <t>D28 31-07-26 @28.4</t>
+        </is>
+      </c>
+      <c r="CE5" s="5" t="inlineStr">
+        <is>
+          <t>07-08-26</t>
+        </is>
+      </c>
+      <c r="CF5" s="5" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="CG5" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="CH5" s="5" t="inlineStr"/>
+      <c r="CI5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-20.93</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-21.65</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-14.64</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>1.8684</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>103526167</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>130019425</v>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 21-05-26</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 21-05-26</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BB6" s="3" t="inlineStr"/>
+      <c r="BC6" s="3" t="inlineStr"/>
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BH6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BI6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BJ6" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BK6" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BL6" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM6" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BN6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BO6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BP6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BQ6" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BR6" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BS6" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BT6" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BU6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BV6" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BW6" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BX6" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BY6" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BZ6" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA6" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC6" s="3" t="inlineStr">
+        <is>
+          <t>T23 23-07-26 @0.95</t>
+        </is>
+      </c>
+      <c r="CD6" s="3" t="inlineStr">
+        <is>
+          <t>D24 11-08-26 @0.83</t>
+        </is>
+      </c>
+      <c r="CE6" s="3" t="inlineStr">
+        <is>
+          <t>17-08-26</t>
+        </is>
+      </c>
+      <c r="CF6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CG6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="CH6" s="3" t="inlineStr"/>
+      <c r="CI6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AAGYO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>-0.3053</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>-11.31</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>-43.41</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>-68.65000000000001</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="Z7" s="5" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AG7" s="5" t="n">
+        <v>19.505</v>
+      </c>
+      <c r="AH7" s="5" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="AI7" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ7" s="5" t="n">
+        <v>6194991</v>
+      </c>
+      <c r="AK7" s="5" t="n">
+        <v>9330204</v>
+      </c>
+      <c r="AL7" s="5" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="AM7" s="5" t="inlineStr"/>
+      <c r="AN7" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+        </is>
+      </c>
+      <c r="AO7" s="5" t="inlineStr"/>
+      <c r="AP7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
+        </is>
+      </c>
+      <c r="AQ7" s="5" t="inlineStr"/>
+      <c r="AR7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
+        </is>
+      </c>
+      <c r="AS7" s="5" t="inlineStr"/>
+      <c r="AT7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 15-04-26</t>
+        </is>
+      </c>
+      <c r="AU7" s="5" t="inlineStr"/>
+      <c r="AV7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 15-04-26</t>
+        </is>
+      </c>
+      <c r="AW7" s="5" t="inlineStr"/>
+      <c r="AX7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 16-04-26</t>
+        </is>
+      </c>
+      <c r="AY7" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ7" s="5" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="BB7" s="5" t="inlineStr"/>
+      <c r="BC7" s="5" t="inlineStr"/>
+      <c r="BD7" s="5" t="inlineStr"/>
+      <c r="BE7" s="5" t="inlineStr"/>
+      <c r="BF7" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BG7" s="5" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="BH7" s="5" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="BI7" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BJ7" s="5" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="BK7" s="5" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="BL7" s="5" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="BM7" s="5" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="BN7" s="5" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="BO7" s="5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="BP7" s="5" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="BQ7" s="5" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="BR7" s="5" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="BS7" s="5" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="BT7" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="BU7" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="BV7" s="5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="BW7" s="5" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="BX7" s="5" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="BY7" s="5" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="BZ7" s="5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="CA7" s="5" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="CB7" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC7" s="5" t="inlineStr">
+        <is>
+          <t>T6 21-08-26 @13.42</t>
+        </is>
+      </c>
+      <c r="CD7" s="5" t="inlineStr">
+        <is>
+          <t>D8 11-08-26 @12.34</t>
+        </is>
+      </c>
+      <c r="CE7" s="5" t="inlineStr">
+        <is>
+          <t>19-08-26</t>
+        </is>
+      </c>
+      <c r="CF7" s="5" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="CG7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="CH7" s="5" t="inlineStr"/>
+      <c r="CI7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>ADGYO</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>2.5196</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>3.0772</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>144.04</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>50.1926</v>
+      </c>
+      <c r="AH8" s="3" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AI8" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>919427</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>1007641</v>
+      </c>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (14-04-26–06-08-26, ~%8.3 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseldi; birikim işareti. OBV 05-08-26 tarihinde önceden kırmıştı.</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14-08-26</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 05-08-26</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17-08-26</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
+        </is>
+      </c>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr"/>
+      <c r="BC8" s="3" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr"/>
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="BH8" s="3" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="BI8" s="3" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="BJ8" s="3" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="BK8" s="3" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="BL8" s="3" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="BM8" s="3" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="BN8" s="3" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="BO8" s="3" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="BP8" s="3" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="BQ8" s="3" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="BR8" s="3" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="BS8" s="3" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="BT8" s="3" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="BU8" s="3" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="BV8" s="3" t="n">
+        <v>68.77</v>
+      </c>
+      <c r="BW8" s="3" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="BX8" s="3" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="BY8" s="3" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="BZ8" s="3" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="CA8" s="3" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="CB8" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC8" s="3" t="inlineStr">
+        <is>
+          <t>T29 25-08-26 @65.85</t>
+        </is>
+      </c>
+      <c r="CD8" s="3" t="inlineStr">
+        <is>
+          <t>D30 13-08-26 @51.1</t>
+        </is>
+      </c>
+      <c r="CE8" s="3" t="inlineStr">
+        <is>
+          <t>17-08-26</t>
+        </is>
+      </c>
+      <c r="CF8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="CG8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="CH8" s="3" t="inlineStr">
+        <is>
+          <t>05-08-26</t>
+        </is>
+      </c>
+      <c r="CI8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Aşağı kırılım</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-0.6385999999999999</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>-0.1405</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>-44.67</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>-41.73</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>-133.9</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>-131.16</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="Z9" s="5" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG9" s="5" t="n">
+        <v>16.9844</v>
+      </c>
+      <c r="AH9" s="5" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AI9" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ9" s="5" t="n">
+        <v>56600577</v>
+      </c>
+      <c r="AK9" s="5" t="n">
+        <v>55223005</v>
+      </c>
+      <c r="AL9" s="5" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN9" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 27-08-26 tarihinde yükselen destek (17-04-26–13-08-26, ~%2.5 yükseliş, 3 temas) çizgisini aşağı kırdı. OBV düşüşte; doğruluyor.</t>
+        </is>
+      </c>
+      <c r="AO9" s="5" t="inlineStr"/>
+      <c r="AP9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 11-08-26</t>
+        </is>
+      </c>
+      <c r="AQ9" s="5" t="inlineStr"/>
+      <c r="AR9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 12-08-26</t>
+        </is>
+      </c>
+      <c r="AS9" s="5" t="inlineStr"/>
+      <c r="AT9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 13-08-26</t>
+        </is>
+      </c>
+      <c r="AU9" s="5" t="inlineStr"/>
+      <c r="AV9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 17-08-26</t>
+        </is>
+      </c>
+      <c r="AW9" s="5" t="inlineStr"/>
+      <c r="AX9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AY9" s="5" t="inlineStr"/>
+      <c r="AZ9" s="5" t="inlineStr"/>
+      <c r="BA9" s="5" t="inlineStr"/>
+      <c r="BB9" s="5" t="inlineStr"/>
+      <c r="BC9" s="5" t="inlineStr"/>
+      <c r="BD9" s="5" t="inlineStr"/>
+      <c r="BE9" s="5" t="inlineStr"/>
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="BH9" s="5" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BI9" s="5" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="BJ9" s="5" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="BK9" s="5" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="BL9" s="5" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="BM9" s="5" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="BN9" s="5" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="BO9" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BP9" s="5" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="BQ9" s="5" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="BR9" s="5" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="BS9" s="5" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="BT9" s="5" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BU9" s="5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="BV9" s="5" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="BW9" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="BX9" s="5" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="BY9" s="5" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="BZ9" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="CA9" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="CB9" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC9" s="5" t="inlineStr">
+        <is>
+          <t>T28 19-08-26 @19.61</t>
+        </is>
+      </c>
+      <c r="CD9" s="5" t="inlineStr">
+        <is>
+          <t>D31 13-08-26 @18.74</t>
+        </is>
+      </c>
+      <c r="CE9" s="5" t="inlineStr">
+        <is>
+          <t>27-08-26</t>
+        </is>
+      </c>
+      <c r="CF9" s="5" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="CG9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH9" s="5" t="inlineStr"/>
+      <c r="CI9" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
+  <autoFilter ref="A1:CI9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -495,12 +3235,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:CI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="5" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="5" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="27" max="27"/>
+    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="7" customWidth="1" min="29" max="29"/>
+    <col width="7" customWidth="1" min="30" max="30"/>
+    <col width="7" customWidth="1" min="31" max="31"/>
+    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="6" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="47" max="47"/>
+    <col width="19" customWidth="1" min="48" max="48"/>
+    <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="19" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="11" customWidth="1" min="53" max="53"/>
+    <col width="11" customWidth="1" min="54" max="54"/>
+    <col width="11" customWidth="1" min="55" max="55"/>
+    <col width="11" customWidth="1" min="56" max="56"/>
+    <col width="19" customWidth="1" min="57" max="57"/>
+    <col width="18" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="11" customWidth="1" min="60" max="60"/>
+    <col width="11" customWidth="1" min="61" max="61"/>
+    <col width="11" customWidth="1" min="62" max="62"/>
+    <col width="11" customWidth="1" min="63" max="63"/>
+    <col width="11" customWidth="1" min="64" max="64"/>
+    <col width="11" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="13" customWidth="1" min="69" max="69"/>
+    <col width="13" customWidth="1" min="70" max="70"/>
+    <col width="13" customWidth="1" min="71" max="71"/>
+    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="11" customWidth="1" min="80" max="80"/>
+    <col width="16" customWidth="1" min="81" max="81"/>
+    <col width="15" customWidth="1" min="82" max="82"/>
+    <col width="16" customWidth="1" min="83" max="83"/>
+    <col width="16" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="13" customWidth="1" min="86" max="86"/>
+    <col width="6" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,17 +3335,437 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Son fiyat</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük %</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Skor</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Hatta uzaklık %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>RSI 14</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>MACD hist</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Momentum %10</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ATR %</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>StochRSI K</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>StochRSI D</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>WT1</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>WT2</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>WT hist</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>SMI</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>SMI sinyal</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>E34</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>E55</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>5x8</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>8x13</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>13x21</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>21x34</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>34x55</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>E fan</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>VWAP fark %</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>Hacim oranı</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>Ort hacim</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>Baz hacim</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>Merdiven</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>Hacim onay</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>Özet</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 5x8</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 5x8</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 8x13</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 8x13</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 13x21</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 13x21</t>
+        </is>
+      </c>
+      <c r="AU1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 21x34</t>
+        </is>
+      </c>
+      <c r="AV1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 21x34</t>
+        </is>
+      </c>
+      <c r="AW1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 34x55</t>
+        </is>
+      </c>
+      <c r="AX1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 34x55</t>
+        </is>
+      </c>
+      <c r="AY1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E5</t>
+        </is>
+      </c>
+      <c r="AZ1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E8</t>
+        </is>
+      </c>
+      <c r="BA1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E13</t>
+        </is>
+      </c>
+      <c r="BB1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E21</t>
+        </is>
+      </c>
+      <c r="BC1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E34</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E55</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>▲ Yukarı kesenler</t>
+        </is>
+      </c>
+      <c r="BF1" s="2" t="inlineStr">
+        <is>
+          <t>▼ Aşağı kesenler</t>
+        </is>
+      </c>
+      <c r="BG1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük P</t>
+        </is>
+      </c>
+      <c r="BH1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R1</t>
+        </is>
+      </c>
+      <c r="BI1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R3</t>
+        </is>
+      </c>
+      <c r="BK1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S1</t>
+        </is>
+      </c>
+      <c r="BL1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S2</t>
+        </is>
+      </c>
+      <c r="BM1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S3</t>
+        </is>
+      </c>
+      <c r="BN1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık P</t>
+        </is>
+      </c>
+      <c r="BO1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R1</t>
+        </is>
+      </c>
+      <c r="BP1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R2</t>
+        </is>
+      </c>
+      <c r="BQ1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R3</t>
+        </is>
+      </c>
+      <c r="BR1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S1</t>
+        </is>
+      </c>
+      <c r="BS1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S2</t>
+        </is>
+      </c>
+      <c r="BT1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S3</t>
+        </is>
+      </c>
+      <c r="BU1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık P</t>
+        </is>
+      </c>
+      <c r="BV1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R1</t>
+        </is>
+      </c>
+      <c r="BW1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R2</t>
+        </is>
+      </c>
+      <c r="BX1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R3</t>
+        </is>
+      </c>
+      <c r="BY1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S1</t>
+        </is>
+      </c>
+      <c r="BZ1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S2</t>
+        </is>
+      </c>
+      <c r="CA1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S3</t>
+        </is>
+      </c>
+      <c r="CB1" s="2" t="inlineStr">
+        <is>
+          <t>Pivot ▲/▼</t>
+        </is>
+      </c>
+      <c r="CC1" s="2" t="inlineStr">
+        <is>
+          <t>Son pivot tepe</t>
+        </is>
+      </c>
+      <c r="CD1" s="2" t="inlineStr">
+        <is>
+          <t>Son pivot dip</t>
+        </is>
+      </c>
+      <c r="CE1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım tarihi</t>
+        </is>
+      </c>
+      <c r="CF1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım fiyatı</t>
+        </is>
+      </c>
+      <c r="CG1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım (gün önce)</t>
+        </is>
+      </c>
+      <c r="CH1" s="2" t="inlineStr">
+        <is>
+          <t>OBV kırılım</t>
+        </is>
+      </c>
+      <c r="CI1" s="2" t="inlineStr">
         <is>
           <t>Hata</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1"/>
+  <autoFilter ref="A1:CI1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -532,12 +3776,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:CI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+    <col width="8" customWidth="1" min="25" max="25"/>
+    <col width="7" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="27" max="27"/>
+    <col width="6" customWidth="1" min="28" max="28"/>
+    <col width="7" customWidth="1" min="29" max="29"/>
+    <col width="7" customWidth="1" min="30" max="30"/>
+    <col width="7" customWidth="1" min="31" max="31"/>
+    <col width="7" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="25" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
+    <col width="18" customWidth="1" min="44" max="44"/>
+    <col width="15" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="46" max="46"/>
+    <col width="15" customWidth="1" min="47" max="47"/>
+    <col width="19" customWidth="1" min="48" max="48"/>
+    <col width="15" customWidth="1" min="49" max="49"/>
+    <col width="19" customWidth="1" min="50" max="50"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="52" max="52"/>
+    <col width="11" customWidth="1" min="53" max="53"/>
+    <col width="11" customWidth="1" min="54" max="54"/>
+    <col width="11" customWidth="1" min="55" max="55"/>
+    <col width="11" customWidth="1" min="56" max="56"/>
+    <col width="19" customWidth="1" min="57" max="57"/>
+    <col width="18" customWidth="1" min="58" max="58"/>
+    <col width="10" customWidth="1" min="59" max="59"/>
+    <col width="11" customWidth="1" min="60" max="60"/>
+    <col width="11" customWidth="1" min="61" max="61"/>
+    <col width="11" customWidth="1" min="62" max="62"/>
+    <col width="11" customWidth="1" min="63" max="63"/>
+    <col width="11" customWidth="1" min="64" max="64"/>
+    <col width="11" customWidth="1" min="65" max="65"/>
+    <col width="12" customWidth="1" min="66" max="66"/>
+    <col width="13" customWidth="1" min="67" max="67"/>
+    <col width="13" customWidth="1" min="68" max="68"/>
+    <col width="13" customWidth="1" min="69" max="69"/>
+    <col width="13" customWidth="1" min="70" max="70"/>
+    <col width="13" customWidth="1" min="71" max="71"/>
+    <col width="13" customWidth="1" min="72" max="72"/>
+    <col width="9" customWidth="1" min="73" max="73"/>
+    <col width="10" customWidth="1" min="74" max="74"/>
+    <col width="10" customWidth="1" min="75" max="75"/>
+    <col width="10" customWidth="1" min="76" max="76"/>
+    <col width="10" customWidth="1" min="77" max="77"/>
+    <col width="10" customWidth="1" min="78" max="78"/>
+    <col width="10" customWidth="1" min="79" max="79"/>
+    <col width="11" customWidth="1" min="80" max="80"/>
+    <col width="21" customWidth="1" min="81" max="81"/>
+    <col width="21" customWidth="1" min="82" max="82"/>
+    <col width="16" customWidth="1" min="83" max="83"/>
+    <col width="16" customWidth="1" min="84" max="84"/>
+    <col width="20" customWidth="1" min="85" max="85"/>
+    <col width="13" customWidth="1" min="86" max="86"/>
+    <col width="8" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,10 +3876,430 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Son fiyat</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük %</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Durum</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Skor</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Hatta uzaklık %</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>RSI 14</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>MACD hist</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Momentum %10</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>ATR %</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>StochRSI K</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>StochRSI D</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>WT1</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>WT2</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>WT hist</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>SMI</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>SMI sinyal</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>E21</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>E34</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>E55</t>
+        </is>
+      </c>
+      <c r="AA1" s="2" t="inlineStr">
+        <is>
+          <t>5x8</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>8x13</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>13x21</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>21x34</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>34x55</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>E fan</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>VWAP</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>VWAP fark %</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>Hacim oranı</t>
+        </is>
+      </c>
+      <c r="AJ1" s="2" t="inlineStr">
+        <is>
+          <t>Ort hacim</t>
+        </is>
+      </c>
+      <c r="AK1" s="2" t="inlineStr">
+        <is>
+          <t>Baz hacim</t>
+        </is>
+      </c>
+      <c r="AL1" s="2" t="inlineStr">
+        <is>
+          <t>Merdiven</t>
+        </is>
+      </c>
+      <c r="AM1" s="2" t="inlineStr">
+        <is>
+          <t>Hacim onay</t>
+        </is>
+      </c>
+      <c r="AN1" s="2" t="inlineStr">
+        <is>
+          <t>Özet</t>
+        </is>
+      </c>
+      <c r="AO1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 5x8</t>
+        </is>
+      </c>
+      <c r="AP1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 5x8</t>
+        </is>
+      </c>
+      <c r="AQ1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 8x13</t>
+        </is>
+      </c>
+      <c r="AR1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 8x13</t>
+        </is>
+      </c>
+      <c r="AS1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 13x21</t>
+        </is>
+      </c>
+      <c r="AT1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 13x21</t>
+        </is>
+      </c>
+      <c r="AU1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 21x34</t>
+        </is>
+      </c>
+      <c r="AV1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 21x34</t>
+        </is>
+      </c>
+      <c r="AW1" s="2" t="inlineStr">
+        <is>
+          <t>Kesişim 34x55</t>
+        </is>
+      </c>
+      <c r="AX1" s="2" t="inlineStr">
+        <is>
+          <t>Son kesişim 34x55</t>
+        </is>
+      </c>
+      <c r="AY1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E5</t>
+        </is>
+      </c>
+      <c r="AZ1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E8</t>
+        </is>
+      </c>
+      <c r="BA1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E13</t>
+        </is>
+      </c>
+      <c r="BB1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E21</t>
+        </is>
+      </c>
+      <c r="BC1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E34</t>
+        </is>
+      </c>
+      <c r="BD1" s="2" t="inlineStr">
+        <is>
+          <t>Kesim E55</t>
+        </is>
+      </c>
+      <c r="BE1" s="2" t="inlineStr">
+        <is>
+          <t>▲ Yukarı kesenler</t>
+        </is>
+      </c>
+      <c r="BF1" s="2" t="inlineStr">
+        <is>
+          <t>▼ Aşağı kesenler</t>
+        </is>
+      </c>
+      <c r="BG1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük P</t>
+        </is>
+      </c>
+      <c r="BH1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R1</t>
+        </is>
+      </c>
+      <c r="BI1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R2</t>
+        </is>
+      </c>
+      <c r="BJ1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük R3</t>
+        </is>
+      </c>
+      <c r="BK1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S1</t>
+        </is>
+      </c>
+      <c r="BL1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S2</t>
+        </is>
+      </c>
+      <c r="BM1" s="2" t="inlineStr">
+        <is>
+          <t>Günlük S3</t>
+        </is>
+      </c>
+      <c r="BN1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık P</t>
+        </is>
+      </c>
+      <c r="BO1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R1</t>
+        </is>
+      </c>
+      <c r="BP1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R2</t>
+        </is>
+      </c>
+      <c r="BQ1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık R3</t>
+        </is>
+      </c>
+      <c r="BR1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S1</t>
+        </is>
+      </c>
+      <c r="BS1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S2</t>
+        </is>
+      </c>
+      <c r="BT1" s="2" t="inlineStr">
+        <is>
+          <t>Haftalık S3</t>
+        </is>
+      </c>
+      <c r="BU1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık P</t>
+        </is>
+      </c>
+      <c r="BV1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R1</t>
+        </is>
+      </c>
+      <c r="BW1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R2</t>
+        </is>
+      </c>
+      <c r="BX1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık R3</t>
+        </is>
+      </c>
+      <c r="BY1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S1</t>
+        </is>
+      </c>
+      <c r="BZ1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S2</t>
+        </is>
+      </c>
+      <c r="CA1" s="2" t="inlineStr">
+        <is>
+          <t>Aylık S3</t>
+        </is>
+      </c>
+      <c r="CB1" s="2" t="inlineStr">
+        <is>
+          <t>Pivot ▲/▼</t>
+        </is>
+      </c>
+      <c r="CC1" s="2" t="inlineStr">
+        <is>
+          <t>Son pivot tepe</t>
+        </is>
+      </c>
+      <c r="CD1" s="2" t="inlineStr">
+        <is>
+          <t>Son pivot dip</t>
+        </is>
+      </c>
+      <c r="CE1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım tarihi</t>
+        </is>
+      </c>
+      <c r="CF1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım fiyatı</t>
+        </is>
+      </c>
+      <c r="CG1" s="2" t="inlineStr">
+        <is>
+          <t>Kırılım (gün önce)</t>
+        </is>
+      </c>
+      <c r="CH1" s="2" t="inlineStr">
+        <is>
+          <t>OBV kırılım</t>
+        </is>
+      </c>
+      <c r="CI1" s="2" t="inlineStr">
         <is>
           <t>Hata</t>
         </is>
@@ -560,175 +4308,2431 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ADEL</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>cannot access local variable 'info' where it is not associated with a value</t>
-        </is>
-      </c>
+          <t>AGESA</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>70.23</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>3.5711</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>2.7738</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>7.6379</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>253.88</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>250.08</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>246.64</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>244.26</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>242.97</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="AA2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE2" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>207.1883</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>264517</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>221633</v>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (15-06-26–06-08-26, ~%3.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 21-08-26 tarihinde önceden kırmıştı.</t>
+        </is>
+      </c>
+      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AP2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
+        </is>
+      </c>
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25-08-26</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26-08-26</t>
+        </is>
+      </c>
+      <c r="AW2" s="3" t="inlineStr"/>
+      <c r="AX2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26-08-26</t>
+        </is>
+      </c>
+      <c r="AY2" s="3" t="inlineStr"/>
+      <c r="AZ2" s="3" t="inlineStr"/>
+      <c r="BA2" s="3" t="inlineStr"/>
+      <c r="BB2" s="3" t="inlineStr"/>
+      <c r="BC2" s="3" t="inlineStr"/>
+      <c r="BD2" s="3" t="inlineStr"/>
+      <c r="BE2" s="3" t="inlineStr"/>
+      <c r="BF2" s="3" t="inlineStr"/>
+      <c r="BG2" s="3" t="n">
+        <v>260.83</v>
+      </c>
+      <c r="BH2" s="3" t="n">
+        <v>264.67</v>
+      </c>
+      <c r="BI2" s="3" t="n">
+        <v>267.33</v>
+      </c>
+      <c r="BJ2" s="3" t="n">
+        <v>271.17</v>
+      </c>
+      <c r="BK2" s="3" t="n">
+        <v>258.17</v>
+      </c>
+      <c r="BL2" s="3" t="n">
+        <v>254.33</v>
+      </c>
+      <c r="BM2" s="3" t="n">
+        <v>251.67</v>
+      </c>
+      <c r="BN2" s="3" t="n">
+        <v>255.53</v>
+      </c>
+      <c r="BO2" s="3" t="n">
+        <v>269.97</v>
+      </c>
+      <c r="BP2" s="3" t="n">
+        <v>277.93</v>
+      </c>
+      <c r="BQ2" s="3" t="n">
+        <v>292.37</v>
+      </c>
+      <c r="BR2" s="3" t="n">
+        <v>247.57</v>
+      </c>
+      <c r="BS2" s="3" t="n">
+        <v>233.13</v>
+      </c>
+      <c r="BT2" s="3" t="n">
+        <v>225.17</v>
+      </c>
+      <c r="BU2" s="3" t="n">
+        <v>251.03</v>
+      </c>
+      <c r="BV2" s="3" t="n">
+        <v>274.47</v>
+      </c>
+      <c r="BW2" s="3" t="n">
+        <v>286.93</v>
+      </c>
+      <c r="BX2" s="3" t="n">
+        <v>310.37</v>
+      </c>
+      <c r="BY2" s="3" t="n">
+        <v>238.57</v>
+      </c>
+      <c r="BZ2" s="3" t="n">
+        <v>215.13</v>
+      </c>
+      <c r="CA2" s="3" t="n">
+        <v>202.67</v>
+      </c>
+      <c r="CB2" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC2" s="3" t="inlineStr">
+        <is>
+          <t>T30 12-08-26 @246.1</t>
+        </is>
+      </c>
+      <c r="CD2" s="3" t="inlineStr">
+        <is>
+          <t>D29 18-08-26 @231.6</t>
+        </is>
+      </c>
+      <c r="CE2" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
+      <c r="CF2" s="3" t="n">
+        <v>251.75</v>
+      </c>
+      <c r="CG2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH2" s="3" t="inlineStr">
+        <is>
+          <t>21-08-26</t>
+        </is>
+      </c>
+      <c r="CI2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>A1CAP</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>name 'tc' is not defined</t>
-        </is>
-      </c>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A1YEN</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>53.79</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>-0.008200000000000001</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0.1086</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>93.92</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y3" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Z3" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AA3" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB3" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE3" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF3" s="5" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AG3" s="5" t="n">
+        <v>3.0427</v>
+      </c>
+      <c r="AH3" s="5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI3" s="5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AJ3" s="5" t="n">
+        <v>23770802</v>
+      </c>
+      <c r="AK3" s="5" t="n">
+        <v>19927913</v>
+      </c>
+      <c r="AL3" s="5" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM3" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN3" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (13-05-26–10-08-26, ~%32.6 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 14-08-26 tarihinde önceden kırmıştı.</t>
+        </is>
+      </c>
+      <c r="AO3" s="5" t="inlineStr"/>
+      <c r="AP3" s="6" t="inlineStr">
+        <is>
+          <t>▲ 14-08-26</t>
+        </is>
+      </c>
+      <c r="AQ3" s="5" t="inlineStr"/>
+      <c r="AR3" s="6" t="inlineStr">
+        <is>
+          <t>▲ 18-08-26</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="inlineStr"/>
+      <c r="AT3" s="7" t="inlineStr">
+        <is>
+          <t>▼ 12-06-26</t>
+        </is>
+      </c>
+      <c r="AU3" s="5" t="inlineStr"/>
+      <c r="AV3" s="7" t="inlineStr">
+        <is>
+          <t>▼ 22-06-26</t>
+        </is>
+      </c>
+      <c r="AW3" s="5" t="inlineStr"/>
+      <c r="AX3" s="7" t="inlineStr">
+        <is>
+          <t>▼ 02-07-26</t>
+        </is>
+      </c>
+      <c r="AY3" s="5" t="inlineStr"/>
+      <c r="AZ3" s="5" t="inlineStr"/>
+      <c r="BA3" s="5" t="inlineStr"/>
+      <c r="BB3" s="5" t="inlineStr"/>
+      <c r="BC3" s="5" t="inlineStr"/>
+      <c r="BD3" s="5" t="inlineStr"/>
+      <c r="BE3" s="5" t="inlineStr"/>
+      <c r="BF3" s="5" t="inlineStr"/>
+      <c r="BG3" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH3" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI3" s="5" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BJ3" s="5" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BK3" s="5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BL3" s="5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BM3" s="5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BN3" s="5" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BO3" s="5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP3" s="5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="BQ3" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BR3" s="5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BS3" s="5" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BT3" s="5" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BU3" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BV3" s="5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="BW3" s="5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BX3" s="5" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="BY3" s="5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BZ3" s="5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CA3" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="CB3" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC3" s="5" t="inlineStr">
+        <is>
+          <t>T29 25-08-26 @2.95</t>
+        </is>
+      </c>
+      <c r="CD3" s="5" t="inlineStr">
+        <is>
+          <t>D30 25-08-26 @2.72</t>
+        </is>
+      </c>
+      <c r="CE3" s="5" t="inlineStr">
+        <is>
+          <t>17-08-26</t>
+        </is>
+      </c>
+      <c r="CF3" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CG3" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="CH3" s="5" t="inlineStr">
+        <is>
+          <t>14-08-26</t>
+        </is>
+      </c>
+      <c r="CI3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>AAGYO</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>name 'tc' is not defined</t>
-        </is>
-      </c>
+          <t>A1CAP</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>47.78</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.2832</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>-24.38</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-36.54</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>-287.49</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-363.06</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>11.1687</v>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>-22.64</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AJ4" s="3" t="n">
+        <v>6736736</v>
+      </c>
+      <c r="AK4" s="3" t="n">
+        <v>7700768</v>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 26-08-26</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 27-03-26</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-04-26</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr"/>
+      <c r="BG4" s="3" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="BH4" s="3" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="BI4" s="3" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="BJ4" s="3" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="BK4" s="3" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="BL4" s="3" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BM4" s="3" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="BN4" s="3" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="BO4" s="3" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="BP4" s="3" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="BQ4" s="3" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="BR4" s="3" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="BS4" s="3" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="BT4" s="3" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BU4" s="3" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="BV4" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BW4" s="3" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="BX4" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BY4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ4" s="3" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="CA4" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="CB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC4" s="3" t="inlineStr">
+        <is>
+          <t>T26 18-08-26 @8.45</t>
+        </is>
+      </c>
+      <c r="CD4" s="3" t="inlineStr">
+        <is>
+          <t>D28 31-07-26 @8.58</t>
+        </is>
+      </c>
+      <c r="CE4" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
+      <c r="CF4" s="3" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="CG4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="CH4" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
+      <c r="CI4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>A1YEN</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>name 'tc' is not defined</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ADEL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>61.33</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.2997</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.7785</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>65.17</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>52.35</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>151.57</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>149.19</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>34.22</v>
+      </c>
+      <c r="X5" s="5" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="Y5" s="5" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="Z5" s="5" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF5" s="5" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="AG5" s="5" t="n">
+        <v>37.0379</v>
+      </c>
+      <c r="AH5" s="5" t="n">
+        <v>-4.31</v>
+      </c>
+      <c r="AI5" s="5" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AJ5" s="5" t="n">
+        <v>10999396</v>
+      </c>
+      <c r="AK5" s="5" t="n">
+        <v>3843601</v>
+      </c>
+      <c r="AL5" s="5" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM5" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN5" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
+        </is>
+      </c>
+      <c r="AO5" s="5" t="inlineStr"/>
+      <c r="AP5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
+        </is>
+      </c>
+      <c r="AQ5" s="5" t="inlineStr"/>
+      <c r="AR5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
+        </is>
+      </c>
+      <c r="AS5" s="5" t="inlineStr"/>
+      <c r="AT5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 12-08-26</t>
+        </is>
+      </c>
+      <c r="AU5" s="5" t="inlineStr"/>
+      <c r="AV5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 20-08-26</t>
+        </is>
+      </c>
+      <c r="AW5" s="5" t="inlineStr"/>
+      <c r="AX5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 02-06-26</t>
+        </is>
+      </c>
+      <c r="AY5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ5" s="5" t="inlineStr"/>
+      <c r="BA5" s="5" t="inlineStr"/>
+      <c r="BB5" s="5" t="inlineStr"/>
+      <c r="BC5" s="5" t="inlineStr"/>
+      <c r="BD5" s="5" t="inlineStr"/>
+      <c r="BE5" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BF5" s="5" t="inlineStr"/>
+      <c r="BG5" s="5" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="BH5" s="5" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="BI5" s="5" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="BJ5" s="5" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="BK5" s="5" t="n">
+        <v>34.73</v>
+      </c>
+      <c r="BL5" s="5" t="n">
+        <v>34.03</v>
+      </c>
+      <c r="BM5" s="5" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="BN5" s="5" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="BO5" s="5" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="BP5" s="5" t="n">
+        <v>41.57</v>
+      </c>
+      <c r="BQ5" s="5" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="BR5" s="5" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="BS5" s="5" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="BT5" s="5" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="BU5" s="5" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="BV5" s="5" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="BW5" s="5" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="BX5" s="5" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="BY5" s="5" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="BZ5" s="5" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="CA5" s="5" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="CB5" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC5" s="5" t="inlineStr">
+        <is>
+          <t>T31 25-08-26 @39.1</t>
+        </is>
+      </c>
+      <c r="CD5" s="5" t="inlineStr">
+        <is>
+          <t>D28 31-07-26 @28.4</t>
+        </is>
+      </c>
+      <c r="CE5" s="5" t="inlineStr">
+        <is>
+          <t>07-08-26</t>
+        </is>
+      </c>
+      <c r="CF5" s="5" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="CG5" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="CH5" s="5" t="inlineStr"/>
+      <c r="CI5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ACSEL</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>cannot access local variable 'info' where it is not associated with a value</t>
-        </is>
-      </c>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.0107</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>51.52</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>-20.93</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-21.65</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-14.64</v>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>1.8684</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>103526167</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>130019425</v>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 21-05-26</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 21-05-26</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BB6" s="3" t="inlineStr"/>
+      <c r="BC6" s="3" t="inlineStr"/>
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BG6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BH6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BI6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BJ6" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BK6" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BL6" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM6" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BN6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BO6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BP6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BQ6" s="3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BR6" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BS6" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BT6" s="3" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BU6" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BV6" s="3" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BW6" s="3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BX6" s="3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BY6" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BZ6" s="3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA6" s="3" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC6" s="3" t="inlineStr">
+        <is>
+          <t>T23 23-07-26 @0.95</t>
+        </is>
+      </c>
+      <c r="CD6" s="3" t="inlineStr">
+        <is>
+          <t>D24 11-08-26 @0.83</t>
+        </is>
+      </c>
+      <c r="CE6" s="3" t="inlineStr">
+        <is>
+          <t>17-08-26</t>
+        </is>
+      </c>
+      <c r="CF6" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CG6" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="CH6" s="3" t="inlineStr"/>
+      <c r="CI6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>AEFES</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>cannot access local variable 'info' where it is not associated with a value</t>
-        </is>
-      </c>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>AAGYO</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>-0.3053</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>-11.31</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>-43.41</v>
+      </c>
+      <c r="T7" s="5" t="n">
+        <v>-68.65000000000001</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="V7" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="Z7" s="5" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="AA7" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF7" s="5" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AG7" s="5" t="n">
+        <v>19.505</v>
+      </c>
+      <c r="AH7" s="5" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="AI7" s="5" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AJ7" s="5" t="n">
+        <v>6194991</v>
+      </c>
+      <c r="AK7" s="5" t="n">
+        <v>9330204</v>
+      </c>
+      <c r="AL7" s="5" t="inlineStr">
+        <is>
+          <t>1/5</t>
+        </is>
+      </c>
+      <c r="AM7" s="5" t="inlineStr"/>
+      <c r="AN7" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+        </is>
+      </c>
+      <c r="AO7" s="5" t="inlineStr"/>
+      <c r="AP7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
+        </is>
+      </c>
+      <c r="AQ7" s="5" t="inlineStr"/>
+      <c r="AR7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
+        </is>
+      </c>
+      <c r="AS7" s="5" t="inlineStr"/>
+      <c r="AT7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 15-04-26</t>
+        </is>
+      </c>
+      <c r="AU7" s="5" t="inlineStr"/>
+      <c r="AV7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 15-04-26</t>
+        </is>
+      </c>
+      <c r="AW7" s="5" t="inlineStr"/>
+      <c r="AX7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 16-04-26</t>
+        </is>
+      </c>
+      <c r="AY7" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ7" s="5" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="BB7" s="5" t="inlineStr"/>
+      <c r="BC7" s="5" t="inlineStr"/>
+      <c r="BD7" s="5" t="inlineStr"/>
+      <c r="BE7" s="5" t="inlineStr"/>
+      <c r="BF7" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BG7" s="5" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="BH7" s="5" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="BI7" s="5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="BJ7" s="5" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="BK7" s="5" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="BL7" s="5" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="BM7" s="5" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="BN7" s="5" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="BO7" s="5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="BP7" s="5" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="BQ7" s="5" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="BR7" s="5" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="BS7" s="5" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="BT7" s="5" t="n">
+        <v>12.35</v>
+      </c>
+      <c r="BU7" s="5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="BV7" s="5" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="BW7" s="5" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="BX7" s="5" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="BY7" s="5" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="BZ7" s="5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="CA7" s="5" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="CB7" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC7" s="5" t="inlineStr">
+        <is>
+          <t>T6 21-08-26 @13.42</t>
+        </is>
+      </c>
+      <c r="CD7" s="5" t="inlineStr">
+        <is>
+          <t>D8 11-08-26 @12.34</t>
+        </is>
+      </c>
+      <c r="CE7" s="5" t="inlineStr">
+        <is>
+          <t>19-08-26</t>
+        </is>
+      </c>
+      <c r="CF7" s="5" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="CG7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="CH7" s="5" t="inlineStr"/>
+      <c r="CI7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>ADESE</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>cannot access local variable 'info' where it is not associated with a value</t>
-        </is>
-      </c>
+          <t>ADGYO</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>2.5196</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>3.0772</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>-5.49</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>144.04</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>61.05</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>59.51</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>5/5</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>50.1926</v>
+      </c>
+      <c r="AH8" s="3" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AI8" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>919427</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>1007641</v>
+      </c>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>4/5</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (14-04-26–06-08-26, ~%8.3 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseldi; birikim işareti. OBV 05-08-26 tarihinde önceden kırmıştı.</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14-08-26</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 05-08-26</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 17-08-26</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
+        </is>
+      </c>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr"/>
+      <c r="BC8" s="3" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr"/>
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="BH8" s="3" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="BI8" s="3" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="BJ8" s="3" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="BK8" s="3" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="BL8" s="3" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="BM8" s="3" t="n">
+        <v>55.37</v>
+      </c>
+      <c r="BN8" s="3" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="BO8" s="3" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="BP8" s="3" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="BQ8" s="3" t="n">
+        <v>72.52</v>
+      </c>
+      <c r="BR8" s="3" t="n">
+        <v>57.22</v>
+      </c>
+      <c r="BS8" s="3" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="BT8" s="3" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="BU8" s="3" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="BV8" s="3" t="n">
+        <v>68.77</v>
+      </c>
+      <c r="BW8" s="3" t="n">
+        <v>76.98</v>
+      </c>
+      <c r="BX8" s="3" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="BY8" s="3" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="BZ8" s="3" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="CA8" s="3" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="CB8" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="CC8" s="3" t="inlineStr">
+        <is>
+          <t>T29 25-08-26 @65.85</t>
+        </is>
+      </c>
+      <c r="CD8" s="3" t="inlineStr">
+        <is>
+          <t>D30 13-08-26 @51.1</t>
+        </is>
+      </c>
+      <c r="CE8" s="3" t="inlineStr">
+        <is>
+          <t>17-08-26</t>
+        </is>
+      </c>
+      <c r="CF8" s="3" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="CG8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="CH8" s="3" t="inlineStr">
+        <is>
+          <t>05-08-26</t>
+        </is>
+      </c>
+      <c r="CI8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>AFYON</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>name 'tc' is not defined</t>
-        </is>
-      </c>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Aşağı kırılım</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-0.6385999999999999</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>-0.1405</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>-44.67</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>-41.73</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>-133.9</v>
+      </c>
+      <c r="T9" s="5" t="n">
+        <v>-131.16</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="V9" s="5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="Y9" s="5" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="Z9" s="5" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AA9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF9" s="5" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG9" s="5" t="n">
+        <v>16.9844</v>
+      </c>
+      <c r="AH9" s="5" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AI9" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ9" s="5" t="n">
+        <v>56600577</v>
+      </c>
+      <c r="AK9" s="5" t="n">
+        <v>55223005</v>
+      </c>
+      <c r="AL9" s="5" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM9" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN9" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 27-08-26 tarihinde yükselen destek (17-04-26–13-08-26, ~%2.5 yükseliş, 3 temas) çizgisini aşağı kırdı. OBV düşüşte; doğruluyor.</t>
+        </is>
+      </c>
+      <c r="AO9" s="5" t="inlineStr"/>
+      <c r="AP9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 11-08-26</t>
+        </is>
+      </c>
+      <c r="AQ9" s="5" t="inlineStr"/>
+      <c r="AR9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 12-08-26</t>
+        </is>
+      </c>
+      <c r="AS9" s="5" t="inlineStr"/>
+      <c r="AT9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 13-08-26</t>
+        </is>
+      </c>
+      <c r="AU9" s="5" t="inlineStr"/>
+      <c r="AV9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 17-08-26</t>
+        </is>
+      </c>
+      <c r="AW9" s="5" t="inlineStr"/>
+      <c r="AX9" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AY9" s="5" t="inlineStr"/>
+      <c r="AZ9" s="5" t="inlineStr"/>
+      <c r="BA9" s="5" t="inlineStr"/>
+      <c r="BB9" s="5" t="inlineStr"/>
+      <c r="BC9" s="5" t="inlineStr"/>
+      <c r="BD9" s="5" t="inlineStr"/>
+      <c r="BE9" s="5" t="inlineStr"/>
+      <c r="BF9" s="5" t="inlineStr"/>
+      <c r="BG9" s="5" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="BH9" s="5" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BI9" s="5" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="BJ9" s="5" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="BK9" s="5" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="BL9" s="5" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="BM9" s="5" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="BN9" s="5" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="BO9" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BP9" s="5" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="BQ9" s="5" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="BR9" s="5" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="BS9" s="5" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="BT9" s="5" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BU9" s="5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="BV9" s="5" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="BW9" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="BX9" s="5" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="BY9" s="5" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="BZ9" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="CA9" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="CB9" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC9" s="5" t="inlineStr">
+        <is>
+          <t>T28 19-08-26 @19.61</t>
+        </is>
+      </c>
+      <c r="CD9" s="5" t="inlineStr">
+        <is>
+          <t>D31 13-08-26 @18.74</t>
+        </is>
+      </c>
+      <c r="CE9" s="5" t="inlineStr">
+        <is>
+          <t>27-08-26</t>
+        </is>
+      </c>
+      <c r="CF9" s="5" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="CG9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH9" s="5" t="inlineStr"/>
+      <c r="CI9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ADGYO</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+          <t>ACSEL</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>HATA</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>name 'tc' is not defined</t>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr"/>
+      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr"/>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr"/>
+      <c r="BC10" s="3" t="inlineStr"/>
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr"/>
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BM10" s="3" t="inlineStr"/>
+      <c r="BN10" s="3" t="inlineStr"/>
+      <c r="BO10" s="3" t="inlineStr"/>
+      <c r="BP10" s="3" t="inlineStr"/>
+      <c r="BQ10" s="3" t="inlineStr"/>
+      <c r="BR10" s="3" t="inlineStr"/>
+      <c r="BS10" s="3" t="inlineStr"/>
+      <c r="BT10" s="3" t="inlineStr"/>
+      <c r="BU10" s="3" t="inlineStr"/>
+      <c r="BV10" s="3" t="inlineStr"/>
+      <c r="BW10" s="3" t="inlineStr"/>
+      <c r="BX10" s="3" t="inlineStr"/>
+      <c r="BY10" s="3" t="inlineStr"/>
+      <c r="BZ10" s="3" t="inlineStr"/>
+      <c r="CA10" s="3" t="inlineStr"/>
+      <c r="CB10" s="3" t="inlineStr"/>
+      <c r="CC10" s="3" t="inlineStr"/>
+      <c r="CD10" s="3" t="inlineStr"/>
+      <c r="CE10" s="3" t="inlineStr"/>
+      <c r="CF10" s="3" t="inlineStr"/>
+      <c r="CG10" s="3" t="inlineStr"/>
+      <c r="CH10" s="3" t="inlineStr"/>
+      <c r="CI10" s="3" t="inlineStr">
+        <is>
+          <t>'kind'</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>AGESA</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>AFYON</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>HATA</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>name 'tc' is not defined</t>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="inlineStr"/>
+      <c r="V11" s="5" t="inlineStr"/>
+      <c r="W11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="inlineStr"/>
+      <c r="Z11" s="5" t="inlineStr"/>
+      <c r="AA11" s="5" t="inlineStr"/>
+      <c r="AB11" s="5" t="inlineStr"/>
+      <c r="AC11" s="5" t="inlineStr"/>
+      <c r="AD11" s="5" t="inlineStr"/>
+      <c r="AE11" s="5" t="inlineStr"/>
+      <c r="AF11" s="5" t="inlineStr"/>
+      <c r="AG11" s="5" t="inlineStr"/>
+      <c r="AH11" s="5" t="inlineStr"/>
+      <c r="AI11" s="5" t="inlineStr"/>
+      <c r="AJ11" s="5" t="inlineStr"/>
+      <c r="AK11" s="5" t="inlineStr"/>
+      <c r="AL11" s="5" t="inlineStr"/>
+      <c r="AM11" s="5" t="inlineStr"/>
+      <c r="AN11" s="5" t="inlineStr"/>
+      <c r="AO11" s="5" t="inlineStr"/>
+      <c r="AP11" s="5" t="inlineStr"/>
+      <c r="AQ11" s="5" t="inlineStr"/>
+      <c r="AR11" s="5" t="inlineStr"/>
+      <c r="AS11" s="5" t="inlineStr"/>
+      <c r="AT11" s="5" t="inlineStr"/>
+      <c r="AU11" s="5" t="inlineStr"/>
+      <c r="AV11" s="5" t="inlineStr"/>
+      <c r="AW11" s="5" t="inlineStr"/>
+      <c r="AX11" s="5" t="inlineStr"/>
+      <c r="AY11" s="5" t="inlineStr"/>
+      <c r="AZ11" s="5" t="inlineStr"/>
+      <c r="BA11" s="5" t="inlineStr"/>
+      <c r="BB11" s="5" t="inlineStr"/>
+      <c r="BC11" s="5" t="inlineStr"/>
+      <c r="BD11" s="5" t="inlineStr"/>
+      <c r="BE11" s="5" t="inlineStr"/>
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="inlineStr"/>
+      <c r="BH11" s="5" t="inlineStr"/>
+      <c r="BI11" s="5" t="inlineStr"/>
+      <c r="BJ11" s="5" t="inlineStr"/>
+      <c r="BK11" s="5" t="inlineStr"/>
+      <c r="BL11" s="5" t="inlineStr"/>
+      <c r="BM11" s="5" t="inlineStr"/>
+      <c r="BN11" s="5" t="inlineStr"/>
+      <c r="BO11" s="5" t="inlineStr"/>
+      <c r="BP11" s="5" t="inlineStr"/>
+      <c r="BQ11" s="5" t="inlineStr"/>
+      <c r="BR11" s="5" t="inlineStr"/>
+      <c r="BS11" s="5" t="inlineStr"/>
+      <c r="BT11" s="5" t="inlineStr"/>
+      <c r="BU11" s="5" t="inlineStr"/>
+      <c r="BV11" s="5" t="inlineStr"/>
+      <c r="BW11" s="5" t="inlineStr"/>
+      <c r="BX11" s="5" t="inlineStr"/>
+      <c r="BY11" s="5" t="inlineStr"/>
+      <c r="BZ11" s="5" t="inlineStr"/>
+      <c r="CA11" s="5" t="inlineStr"/>
+      <c r="CB11" s="5" t="inlineStr"/>
+      <c r="CC11" s="5" t="inlineStr"/>
+      <c r="CD11" s="5" t="inlineStr"/>
+      <c r="CE11" s="5" t="inlineStr"/>
+      <c r="CF11" s="5" t="inlineStr"/>
+      <c r="CG11" s="5" t="inlineStr"/>
+      <c r="CH11" s="5" t="inlineStr"/>
+      <c r="CI11" s="5" t="inlineStr">
+        <is>
+          <t>'kind'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C11"/>
+  <autoFilter ref="A1:CI11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/ObvTarama_Gunluk_28082026_06:00.xlsx
+++ b/ObvTarama_Gunluk_28082026_06:00.xlsx
@@ -2118,14 +2118,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.99</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.16</v>
+        <v>-1.07</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -2136,236 +2136,232 @@
         <v>80</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6.1</v>
+        <v>10.41</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>47.84</v>
+        <v>43.17</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.0107</v>
+        <v>-0.3053</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.1574</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.031</v>
+        <v>0.378</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.56</v>
+        <v>2.91</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>30.22</v>
+        <v>30.77</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>51.52</v>
+        <v>95.64</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>46.08</v>
+        <v>96.08</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-20.93</v>
+        <v>-4.75</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-21.65</v>
+        <v>-11.31</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.72</v>
+        <v>6.57</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.73</v>
+        <v>-43.41</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-14.64</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.86</v>
+        <v>13.03</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.86</v>
+        <v>12.99</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.98</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.87</v>
+        <v>13.12</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.58</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.91</v>
+        <v>14.49</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>1.8684</v>
+        <v>19.505</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-53.44</v>
+        <v>-33.4</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>103526167</v>
+        <v>6194991</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>130019425</v>
+        <v>9330204</v>
       </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AR6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr"/>
       <c r="AT6" s="8" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr"/>
       <c r="AV6" s="8" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="AZ6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="BA6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="AX6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 16-04-26</t>
+        </is>
+      </c>
+      <c r="AY6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
       <c r="BB6" s="3" t="inlineStr"/>
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>5-8-13</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="BG6" s="3" t="n">
-        <v>0.87</v>
+        <v>13.06</v>
       </c>
       <c r="BH6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.15</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>0.91</v>
+        <v>13.3</v>
       </c>
       <c r="BJ6" s="3" t="n">
-        <v>0.93</v>
+        <v>13.39</v>
       </c>
       <c r="BK6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.91</v>
       </c>
       <c r="BL6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.82</v>
       </c>
       <c r="BM6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.67</v>
       </c>
       <c r="BN6" s="3" t="n">
-        <v>0.87</v>
+        <v>13.08</v>
       </c>
       <c r="BO6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.27</v>
       </c>
       <c r="BP6" s="3" t="n">
-        <v>0.91</v>
+        <v>13.54</v>
       </c>
       <c r="BQ6" s="3" t="n">
-        <v>0.93</v>
+        <v>13.73</v>
       </c>
       <c r="BR6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.81</v>
       </c>
       <c r="BS6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.62</v>
       </c>
       <c r="BT6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.35</v>
       </c>
       <c r="BU6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.95</v>
       </c>
       <c r="BV6" s="3" t="n">
-        <v>0.92</v>
+        <v>13.55</v>
       </c>
       <c r="BW6" s="3" t="n">
-        <v>0.96</v>
+        <v>14.12</v>
       </c>
       <c r="BX6" s="3" t="n">
-        <v>1.01</v>
+        <v>14.72</v>
       </c>
       <c r="BY6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.38</v>
       </c>
       <c r="BZ6" s="3" t="n">
-        <v>0.78</v>
+        <v>11.78</v>
       </c>
       <c r="CA6" s="3" t="n">
-        <v>0.74</v>
+        <v>11.21</v>
       </c>
       <c r="CB6" s="8" t="inlineStr">
         <is>
@@ -2374,24 +2370,24 @@
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>T23 23-07-26 @0.95</t>
+          <t>T6 21-08-26 @13.42</t>
         </is>
       </c>
       <c r="CD6" s="3" t="inlineStr">
         <is>
-          <t>D24 11-08-26 @0.83</t>
+          <t>D8 11-08-26 @12.34</t>
         </is>
       </c>
       <c r="CE6" s="3" t="inlineStr">
         <is>
-          <t>17-08-26</t>
+          <t>19-08-26</t>
         </is>
       </c>
       <c r="CF6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.72</v>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CH6" s="3" t="inlineStr"/>
       <c r="CI6" s="3" t="inlineStr"/>
@@ -2399,14 +2395,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>12.99</v>
+        <v>0.87</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-1.07</v>
+        <v>1.16</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -2417,76 +2413,76 @@
         <v>80</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>10.41</v>
+        <v>6.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>43.17</v>
+        <v>47.84</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.3053</v>
+        <v>-0.0107</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.1574</v>
+        <v>0.0032</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.378</v>
+        <v>0.031</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2.91</v>
+        <v>3.56</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>30.77</v>
+        <v>30.22</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>95.64</v>
+        <v>51.52</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>96.08</v>
+        <v>46.08</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4.75</v>
+        <v>-20.93</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>-11.31</v>
+        <v>-21.65</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>6.57</v>
+        <v>0.72</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-43.41</v>
+        <v>-3.73</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>-68.65000000000001</v>
+        <v>-14.64</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>13.03</v>
+        <v>0.86</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>12.99</v>
+        <v>0.86</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>12.98</v>
+        <v>0.87</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>13.12</v>
+        <v>0.87</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>13.58</v>
+        <v>0.89</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>14.49</v>
+        <v>0.91</v>
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AB7" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC7" s="5" t="inlineStr">
@@ -2506,143 +2502,147 @@
       </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG7" s="5" t="n">
+        <v>1.8684</v>
+      </c>
+      <c r="AH7" s="5" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AI7" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ7" s="5" t="n">
+        <v>103526167</v>
+      </c>
+      <c r="AK7" s="5" t="n">
+        <v>130019425</v>
+      </c>
+      <c r="AL7" s="5" t="inlineStr">
+        <is>
           <t>2/5</t>
-        </is>
-      </c>
-      <c r="AG7" s="5" t="n">
-        <v>19.505</v>
-      </c>
-      <c r="AH7" s="5" t="n">
-        <v>-33.4</v>
-      </c>
-      <c r="AI7" s="5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AJ7" s="5" t="n">
-        <v>6194991</v>
-      </c>
-      <c r="AK7" s="5" t="n">
-        <v>9330204</v>
-      </c>
-      <c r="AL7" s="5" t="inlineStr">
-        <is>
-          <t>1/5</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr"/>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr"/>
-      <c r="AP7" s="6" t="inlineStr">
-        <is>
-          <t>▲ 21-08-26</t>
+      <c r="AP7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AQ7" s="5" t="inlineStr"/>
-      <c r="AR7" s="6" t="inlineStr">
-        <is>
-          <t>▲ 27-08-26</t>
+      <c r="AR7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AS7" s="5" t="inlineStr"/>
       <c r="AT7" s="7" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AU7" s="5" t="inlineStr"/>
       <c r="AV7" s="7" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AW7" s="5" t="inlineStr"/>
-      <c r="AX7" s="7" t="inlineStr">
-        <is>
-          <t>▼ 16-04-26</t>
-        </is>
-      </c>
-      <c r="AY7" s="7" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="AZ7" s="5" t="inlineStr"/>
-      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="AX7" s="5" t="inlineStr"/>
+      <c r="AY7" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ7" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA7" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BB7" s="5" t="inlineStr"/>
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
-      <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="BE7" s="5" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
+      <c r="BF7" s="5" t="inlineStr"/>
       <c r="BG7" s="5" t="n">
-        <v>13.06</v>
+        <v>0.87</v>
       </c>
       <c r="BH7" s="5" t="n">
-        <v>13.15</v>
+        <v>0.89</v>
       </c>
       <c r="BI7" s="5" t="n">
-        <v>13.3</v>
+        <v>0.91</v>
       </c>
       <c r="BJ7" s="5" t="n">
-        <v>13.39</v>
+        <v>0.93</v>
       </c>
       <c r="BK7" s="5" t="n">
-        <v>12.91</v>
+        <v>0.85</v>
       </c>
       <c r="BL7" s="5" t="n">
-        <v>12.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM7" s="5" t="n">
-        <v>12.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN7" s="5" t="n">
-        <v>13.08</v>
+        <v>0.87</v>
       </c>
       <c r="BO7" s="5" t="n">
-        <v>13.27</v>
+        <v>0.89</v>
       </c>
       <c r="BP7" s="5" t="n">
-        <v>13.54</v>
+        <v>0.91</v>
       </c>
       <c r="BQ7" s="5" t="n">
-        <v>13.73</v>
+        <v>0.93</v>
       </c>
       <c r="BR7" s="5" t="n">
-        <v>12.81</v>
+        <v>0.85</v>
       </c>
       <c r="BS7" s="5" t="n">
-        <v>12.62</v>
+        <v>0.83</v>
       </c>
       <c r="BT7" s="5" t="n">
-        <v>12.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BU7" s="5" t="n">
-        <v>12.95</v>
+        <v>0.87</v>
       </c>
       <c r="BV7" s="5" t="n">
-        <v>13.55</v>
+        <v>0.92</v>
       </c>
       <c r="BW7" s="5" t="n">
-        <v>14.12</v>
+        <v>0.96</v>
       </c>
       <c r="BX7" s="5" t="n">
-        <v>14.72</v>
+        <v>1.01</v>
       </c>
       <c r="BY7" s="5" t="n">
-        <v>12.38</v>
+        <v>0.83</v>
       </c>
       <c r="BZ7" s="5" t="n">
-        <v>11.78</v>
+        <v>0.78</v>
       </c>
       <c r="CA7" s="5" t="n">
-        <v>11.21</v>
+        <v>0.74</v>
       </c>
       <c r="CB7" s="7" t="inlineStr">
         <is>
@@ -2651,24 +2651,24 @@
       </c>
       <c r="CC7" s="5" t="inlineStr">
         <is>
-          <t>T6 21-08-26 @13.42</t>
+          <t>T23 23-07-26 @0.95</t>
         </is>
       </c>
       <c r="CD7" s="5" t="inlineStr">
         <is>
-          <t>D8 11-08-26 @12.34</t>
+          <t>D24 11-08-26 @0.83</t>
         </is>
       </c>
       <c r="CE7" s="5" t="inlineStr">
         <is>
-          <t>19-08-26</t>
+          <t>17-08-26</t>
         </is>
       </c>
       <c r="CF7" s="5" t="n">
-        <v>12.72</v>
+        <v>0.91</v>
       </c>
       <c r="CG7" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CH7" s="5" t="inlineStr"/>
       <c r="CI7" s="5" t="inlineStr"/>
@@ -5424,14 +5424,14 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.99</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.16</v>
+        <v>-1.07</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -5442,236 +5442,232 @@
         <v>80</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6.1</v>
+        <v>10.41</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>47.84</v>
+        <v>43.17</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.0107</v>
+        <v>-0.3053</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.1574</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.031</v>
+        <v>0.378</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.56</v>
+        <v>2.91</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>30.22</v>
+        <v>30.77</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>51.52</v>
+        <v>95.64</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>46.08</v>
+        <v>96.08</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-20.93</v>
+        <v>-4.75</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-21.65</v>
+        <v>-11.31</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.72</v>
+        <v>6.57</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.73</v>
+        <v>-43.41</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-14.64</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.86</v>
+        <v>13.03</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.86</v>
+        <v>12.99</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.98</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.87</v>
+        <v>13.12</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.58</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.91</v>
+        <v>14.49</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AD6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>1.8684</v>
+        <v>19.505</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-53.44</v>
+        <v>-33.4</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>103526167</v>
+        <v>6194991</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>130019425</v>
+        <v>9330204</v>
       </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AR6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr"/>
       <c r="AT6" s="8" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr"/>
       <c r="AV6" s="8" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="AZ6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="BA6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="AX6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 16-04-26</t>
+        </is>
+      </c>
+      <c r="AY6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
       <c r="BB6" s="3" t="inlineStr"/>
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>5-8-13</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="BG6" s="3" t="n">
-        <v>0.87</v>
+        <v>13.06</v>
       </c>
       <c r="BH6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.15</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>0.91</v>
+        <v>13.3</v>
       </c>
       <c r="BJ6" s="3" t="n">
-        <v>0.93</v>
+        <v>13.39</v>
       </c>
       <c r="BK6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.91</v>
       </c>
       <c r="BL6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.82</v>
       </c>
       <c r="BM6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.67</v>
       </c>
       <c r="BN6" s="3" t="n">
-        <v>0.87</v>
+        <v>13.08</v>
       </c>
       <c r="BO6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.27</v>
       </c>
       <c r="BP6" s="3" t="n">
-        <v>0.91</v>
+        <v>13.54</v>
       </c>
       <c r="BQ6" s="3" t="n">
-        <v>0.93</v>
+        <v>13.73</v>
       </c>
       <c r="BR6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.81</v>
       </c>
       <c r="BS6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.62</v>
       </c>
       <c r="BT6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.35</v>
       </c>
       <c r="BU6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.95</v>
       </c>
       <c r="BV6" s="3" t="n">
-        <v>0.92</v>
+        <v>13.55</v>
       </c>
       <c r="BW6" s="3" t="n">
-        <v>0.96</v>
+        <v>14.12</v>
       </c>
       <c r="BX6" s="3" t="n">
-        <v>1.01</v>
+        <v>14.72</v>
       </c>
       <c r="BY6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.38</v>
       </c>
       <c r="BZ6" s="3" t="n">
-        <v>0.78</v>
+        <v>11.78</v>
       </c>
       <c r="CA6" s="3" t="n">
-        <v>0.74</v>
+        <v>11.21</v>
       </c>
       <c r="CB6" s="8" t="inlineStr">
         <is>
@@ -5680,24 +5676,24 @@
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>T23 23-07-26 @0.95</t>
+          <t>T6 21-08-26 @13.42</t>
         </is>
       </c>
       <c r="CD6" s="3" t="inlineStr">
         <is>
-          <t>D24 11-08-26 @0.83</t>
+          <t>D8 11-08-26 @12.34</t>
         </is>
       </c>
       <c r="CE6" s="3" t="inlineStr">
         <is>
-          <t>17-08-26</t>
+          <t>19-08-26</t>
         </is>
       </c>
       <c r="CF6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.72</v>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CH6" s="3" t="inlineStr"/>
       <c r="CI6" s="3" t="inlineStr"/>
@@ -5705,14 +5701,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>12.99</v>
+        <v>0.87</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-1.07</v>
+        <v>1.16</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -5723,76 +5719,76 @@
         <v>80</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>10.41</v>
+        <v>6.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>43.17</v>
+        <v>47.84</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.3053</v>
+        <v>-0.0107</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.1574</v>
+        <v>0.0032</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.378</v>
+        <v>0.031</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2.91</v>
+        <v>3.56</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>30.77</v>
+        <v>30.22</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>95.64</v>
+        <v>51.52</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>96.08</v>
+        <v>46.08</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4.75</v>
+        <v>-20.93</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>-11.31</v>
+        <v>-21.65</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>6.57</v>
+        <v>0.72</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-43.41</v>
+        <v>-3.73</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>-68.65000000000001</v>
+        <v>-14.64</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>13.03</v>
+        <v>0.86</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>12.99</v>
+        <v>0.86</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>12.98</v>
+        <v>0.87</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>13.12</v>
+        <v>0.87</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>13.58</v>
+        <v>0.89</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>14.49</v>
+        <v>0.91</v>
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AB7" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC7" s="5" t="inlineStr">
@@ -5812,143 +5808,147 @@
       </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG7" s="5" t="n">
+        <v>1.8684</v>
+      </c>
+      <c r="AH7" s="5" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AI7" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ7" s="5" t="n">
+        <v>103526167</v>
+      </c>
+      <c r="AK7" s="5" t="n">
+        <v>130019425</v>
+      </c>
+      <c r="AL7" s="5" t="inlineStr">
+        <is>
           <t>2/5</t>
-        </is>
-      </c>
-      <c r="AG7" s="5" t="n">
-        <v>19.505</v>
-      </c>
-      <c r="AH7" s="5" t="n">
-        <v>-33.4</v>
-      </c>
-      <c r="AI7" s="5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AJ7" s="5" t="n">
-        <v>6194991</v>
-      </c>
-      <c r="AK7" s="5" t="n">
-        <v>9330204</v>
-      </c>
-      <c r="AL7" s="5" t="inlineStr">
-        <is>
-          <t>1/5</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr"/>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr"/>
-      <c r="AP7" s="6" t="inlineStr">
-        <is>
-          <t>▲ 21-08-26</t>
+      <c r="AP7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AQ7" s="5" t="inlineStr"/>
-      <c r="AR7" s="6" t="inlineStr">
-        <is>
-          <t>▲ 27-08-26</t>
+      <c r="AR7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AS7" s="5" t="inlineStr"/>
       <c r="AT7" s="7" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AU7" s="5" t="inlineStr"/>
       <c r="AV7" s="7" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AW7" s="5" t="inlineStr"/>
-      <c r="AX7" s="7" t="inlineStr">
-        <is>
-          <t>▼ 16-04-26</t>
-        </is>
-      </c>
-      <c r="AY7" s="7" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="AZ7" s="5" t="inlineStr"/>
-      <c r="BA7" s="5" t="inlineStr"/>
+      <c r="AX7" s="5" t="inlineStr"/>
+      <c r="AY7" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ7" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA7" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BB7" s="5" t="inlineStr"/>
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
-      <c r="BE7" s="5" t="inlineStr"/>
-      <c r="BF7" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="BE7" s="5" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
+      <c r="BF7" s="5" t="inlineStr"/>
       <c r="BG7" s="5" t="n">
-        <v>13.06</v>
+        <v>0.87</v>
       </c>
       <c r="BH7" s="5" t="n">
-        <v>13.15</v>
+        <v>0.89</v>
       </c>
       <c r="BI7" s="5" t="n">
-        <v>13.3</v>
+        <v>0.91</v>
       </c>
       <c r="BJ7" s="5" t="n">
-        <v>13.39</v>
+        <v>0.93</v>
       </c>
       <c r="BK7" s="5" t="n">
-        <v>12.91</v>
+        <v>0.85</v>
       </c>
       <c r="BL7" s="5" t="n">
-        <v>12.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM7" s="5" t="n">
-        <v>12.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN7" s="5" t="n">
-        <v>13.08</v>
+        <v>0.87</v>
       </c>
       <c r="BO7" s="5" t="n">
-        <v>13.27</v>
+        <v>0.89</v>
       </c>
       <c r="BP7" s="5" t="n">
-        <v>13.54</v>
+        <v>0.91</v>
       </c>
       <c r="BQ7" s="5" t="n">
-        <v>13.73</v>
+        <v>0.93</v>
       </c>
       <c r="BR7" s="5" t="n">
-        <v>12.81</v>
+        <v>0.85</v>
       </c>
       <c r="BS7" s="5" t="n">
-        <v>12.62</v>
+        <v>0.83</v>
       </c>
       <c r="BT7" s="5" t="n">
-        <v>12.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BU7" s="5" t="n">
-        <v>12.95</v>
+        <v>0.87</v>
       </c>
       <c r="BV7" s="5" t="n">
-        <v>13.55</v>
+        <v>0.92</v>
       </c>
       <c r="BW7" s="5" t="n">
-        <v>14.12</v>
+        <v>0.96</v>
       </c>
       <c r="BX7" s="5" t="n">
-        <v>14.72</v>
+        <v>1.01</v>
       </c>
       <c r="BY7" s="5" t="n">
-        <v>12.38</v>
+        <v>0.83</v>
       </c>
       <c r="BZ7" s="5" t="n">
-        <v>11.78</v>
+        <v>0.78</v>
       </c>
       <c r="CA7" s="5" t="n">
-        <v>11.21</v>
+        <v>0.74</v>
       </c>
       <c r="CB7" s="7" t="inlineStr">
         <is>
@@ -5957,24 +5957,24 @@
       </c>
       <c r="CC7" s="5" t="inlineStr">
         <is>
-          <t>T6 21-08-26 @13.42</t>
+          <t>T23 23-07-26 @0.95</t>
         </is>
       </c>
       <c r="CD7" s="5" t="inlineStr">
         <is>
-          <t>D8 11-08-26 @12.34</t>
+          <t>D24 11-08-26 @0.83</t>
         </is>
       </c>
       <c r="CE7" s="5" t="inlineStr">
         <is>
-          <t>19-08-26</t>
+          <t>17-08-26</t>
         </is>
       </c>
       <c r="CF7" s="5" t="n">
-        <v>12.72</v>
+        <v>0.91</v>
       </c>
       <c r="CG7" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CH7" s="5" t="inlineStr"/>
       <c r="CI7" s="5" t="inlineStr"/>
@@ -6532,7 +6532,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>AFYON</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr"/>
@@ -6633,7 +6633,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>AFYON</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>

--- a/ObvTarama_Gunluk_28082026_06:00.xlsx
+++ b/ObvTarama_Gunluk_28082026_06:00.xlsx
@@ -1552,14 +1552,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>35.44</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.86</v>
+        <v>1.72</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -1570,67 +1570,67 @@
         <v>94</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7.98</v>
+        <v>23.15</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>47.78</v>
+        <v>61.33</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.2832</v>
+        <v>1.2997</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.099</v>
+        <v>0.3751</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>7.73</v>
+        <v>6.94</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.2781</v>
+        <v>1.7785</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>3.22</v>
+        <v>5.02</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>22.59</v>
+        <v>37.93</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>39.34</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>65.17</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-24.38</v>
+        <v>52.35</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-36.54</v>
+        <v>53.21</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>12.15</v>
+        <v>-0.86</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-287.49</v>
+        <v>151.57</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-363.06</v>
+        <v>149.19</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>8.44</v>
+        <v>35.39</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>8.4</v>
+        <v>34.96</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>8.42</v>
+        <v>34.22</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>8.57</v>
+        <v>33.37</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>8.9</v>
+        <v>32.81</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.460000000000001</v>
+        <v>32.91</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>11.1687</v>
+        <v>37.0379</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-22.64</v>
+        <v>-4.31</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>0.87</v>
+        <v>2.86</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>6736736</v>
+        <v>10999396</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>7700768</v>
+        <v>3843601</v>
       </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1689,162 +1689,158 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
+          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="4" t="inlineStr">
         <is>
-          <t>▲ 26-08-26</t>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="8" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="8" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AT4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12-08-26</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="8" t="inlineStr">
-        <is>
-          <t>▼ 27-03-26</t>
+      <c r="AV4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20-08-26</t>
         </is>
       </c>
       <c r="AW4" s="3" t="inlineStr"/>
       <c r="AX4" s="8" t="inlineStr">
         <is>
-          <t>▼ 24-04-26</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr"/>
+          <t>▼ 02-06-26</t>
+        </is>
+      </c>
+      <c r="AY4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="AZ4" s="3" t="inlineStr"/>
       <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="BB4" s="3" t="inlineStr"/>
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BF4" s="3" t="inlineStr"/>
       <c r="BG4" s="3" t="n">
-        <v>8.550000000000001</v>
+        <v>35.57</v>
       </c>
       <c r="BH4" s="3" t="n">
-        <v>8.73</v>
+        <v>36.27</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>8.81</v>
+        <v>37.11</v>
       </c>
       <c r="BJ4" s="3" t="n">
-        <v>8.99</v>
+        <v>37.81</v>
       </c>
       <c r="BK4" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>34.73</v>
       </c>
       <c r="BL4" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>34.03</v>
       </c>
       <c r="BM4" s="3" t="n">
-        <v>8.210000000000001</v>
+        <v>33.19</v>
       </c>
       <c r="BN4" s="3" t="n">
-        <v>8.49</v>
+        <v>36.03</v>
       </c>
       <c r="BO4" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>38.51</v>
       </c>
       <c r="BP4" s="3" t="n">
-        <v>8.94</v>
+        <v>41.57</v>
       </c>
       <c r="BQ4" s="3" t="n">
-        <v>9.24</v>
+        <v>44.05</v>
       </c>
       <c r="BR4" s="3" t="n">
-        <v>8.34</v>
+        <v>32.97</v>
       </c>
       <c r="BS4" s="3" t="n">
-        <v>8.039999999999999</v>
+        <v>30.49</v>
       </c>
       <c r="BT4" s="3" t="n">
-        <v>7.89</v>
+        <v>27.43</v>
       </c>
       <c r="BU4" s="3" t="n">
-        <v>8.66</v>
+        <v>34.31</v>
       </c>
       <c r="BV4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>40.23</v>
       </c>
       <c r="BW4" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>45.01</v>
       </c>
       <c r="BX4" s="3" t="n">
-        <v>10.6</v>
+        <v>50.93</v>
       </c>
       <c r="BY4" s="3" t="n">
-        <v>8</v>
+        <v>29.53</v>
       </c>
       <c r="BZ4" s="3" t="n">
-        <v>7.36</v>
+        <v>23.61</v>
       </c>
       <c r="CA4" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="CB4" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
+        <v>18.83</v>
+      </c>
+      <c r="CB4" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="CC4" s="3" t="inlineStr">
         <is>
-          <t>T26 18-08-26 @8.45</t>
+          <t>T31 25-08-26 @39.1</t>
         </is>
       </c>
       <c r="CD4" s="3" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @8.58</t>
+          <t>D28 31-07-26 @28.4</t>
         </is>
       </c>
       <c r="CE4" s="3" t="inlineStr">
         <is>
-          <t>26-08-26</t>
+          <t>07-08-26</t>
         </is>
       </c>
       <c r="CF4" s="3" t="n">
-        <v>8.43</v>
+        <v>32.42</v>
       </c>
       <c r="CG4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CH4" s="3" t="inlineStr">
-        <is>
-          <t>26-08-26</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="CH4" s="3" t="inlineStr"/>
       <c r="CI4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>A1CAP</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>35.44</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1.72</v>
+        <v>2.86</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1855,67 +1851,67 @@
         <v>94</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>23.15</v>
+        <v>7.98</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>61.33</v>
+        <v>47.78</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1.2997</v>
+        <v>-0.2832</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.3751</v>
+        <v>0.099</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>6.94</v>
+        <v>7.73</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1.7785</v>
+        <v>0.2781</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>5.02</v>
+        <v>3.22</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>37.93</v>
+        <v>22.59</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>39.34</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>65.17</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>52.35</v>
+        <v>-24.38</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>53.21</v>
+        <v>-36.54</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>-0.86</v>
+        <v>12.15</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>151.57</v>
+        <v>-287.49</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>149.19</v>
+        <v>-363.06</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>35.39</v>
+        <v>8.44</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>34.96</v>
+        <v>8.4</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>34.22</v>
+        <v>8.42</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>33.37</v>
+        <v>8.57</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>32.81</v>
+        <v>8.9</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>32.91</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AA5" s="5" t="inlineStr">
         <is>
@@ -1924,17 +1920,17 @@
       </c>
       <c r="AB5" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC5" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD5" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
@@ -1944,27 +1940,27 @@
       </c>
       <c r="AF5" s="5" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>37.0379</v>
+        <v>11.1687</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>-4.31</v>
+        <v>-22.64</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>2.86</v>
+        <v>0.87</v>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>10999396</v>
+        <v>6736736</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>3843601</v>
+        <v>7700768</v>
       </c>
       <c r="AL5" s="5" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="AM5" s="5" t="inlineStr">
@@ -1974,158 +1970,162 @@
       </c>
       <c r="AN5" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
         </is>
       </c>
       <c r="AO5" s="5" t="inlineStr"/>
       <c r="AP5" s="6" t="inlineStr">
         <is>
-          <t>▲ 07-08-26</t>
+          <t>▲ 26-08-26</t>
         </is>
       </c>
       <c r="AQ5" s="5" t="inlineStr"/>
-      <c r="AR5" s="6" t="inlineStr">
-        <is>
-          <t>▲ 07-08-26</t>
+      <c r="AR5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AS5" s="5" t="inlineStr"/>
-      <c r="AT5" s="6" t="inlineStr">
-        <is>
-          <t>▲ 12-08-26</t>
+      <c r="AT5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AU5" s="5" t="inlineStr"/>
-      <c r="AV5" s="6" t="inlineStr">
-        <is>
-          <t>▲ 20-08-26</t>
+      <c r="AV5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 27-03-26</t>
         </is>
       </c>
       <c r="AW5" s="5" t="inlineStr"/>
       <c r="AX5" s="7" t="inlineStr">
         <is>
-          <t>▼ 02-06-26</t>
-        </is>
-      </c>
-      <c r="AY5" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+          <t>▼ 24-04-26</t>
+        </is>
+      </c>
+      <c r="AY5" s="5" t="inlineStr"/>
       <c r="AZ5" s="5" t="inlineStr"/>
       <c r="BA5" s="5" t="inlineStr"/>
-      <c r="BB5" s="5" t="inlineStr"/>
+      <c r="BB5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BF5" s="5" t="inlineStr"/>
       <c r="BG5" s="5" t="n">
-        <v>35.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BH5" s="5" t="n">
-        <v>36.27</v>
+        <v>8.73</v>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>37.11</v>
+        <v>8.81</v>
       </c>
       <c r="BJ5" s="5" t="n">
-        <v>37.81</v>
+        <v>8.99</v>
       </c>
       <c r="BK5" s="5" t="n">
-        <v>34.73</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BL5" s="5" t="n">
-        <v>34.03</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BM5" s="5" t="n">
-        <v>33.19</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BN5" s="5" t="n">
-        <v>36.03</v>
+        <v>8.49</v>
       </c>
       <c r="BO5" s="5" t="n">
-        <v>38.51</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BP5" s="5" t="n">
-        <v>41.57</v>
+        <v>8.94</v>
       </c>
       <c r="BQ5" s="5" t="n">
-        <v>44.05</v>
+        <v>9.24</v>
       </c>
       <c r="BR5" s="5" t="n">
-        <v>32.97</v>
+        <v>8.34</v>
       </c>
       <c r="BS5" s="5" t="n">
-        <v>30.49</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BT5" s="5" t="n">
-        <v>27.43</v>
+        <v>7.89</v>
       </c>
       <c r="BU5" s="5" t="n">
-        <v>34.31</v>
+        <v>8.66</v>
       </c>
       <c r="BV5" s="5" t="n">
-        <v>40.23</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BW5" s="5" t="n">
-        <v>45.01</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BX5" s="5" t="n">
-        <v>50.93</v>
+        <v>10.6</v>
       </c>
       <c r="BY5" s="5" t="n">
-        <v>29.53</v>
+        <v>8</v>
       </c>
       <c r="BZ5" s="5" t="n">
-        <v>23.61</v>
+        <v>7.36</v>
       </c>
       <c r="CA5" s="5" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="CB5" s="7" t="inlineStr">
-        <is>
-          <t>▼</t>
+        <v>6.7</v>
+      </c>
+      <c r="CB5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
         </is>
       </c>
       <c r="CC5" s="5" t="inlineStr">
         <is>
-          <t>T31 25-08-26 @39.1</t>
+          <t>T26 18-08-26 @8.45</t>
         </is>
       </c>
       <c r="CD5" s="5" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @28.4</t>
+          <t>D28 31-07-26 @8.58</t>
         </is>
       </c>
       <c r="CE5" s="5" t="inlineStr">
         <is>
-          <t>07-08-26</t>
+          <t>26-08-26</t>
         </is>
       </c>
       <c r="CF5" s="5" t="n">
-        <v>32.42</v>
+        <v>8.43</v>
       </c>
       <c r="CG5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="CH5" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="CH5" s="5" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
       <c r="CI5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12.99</v>
+        <v>0.87</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-1.07</v>
+        <v>1.16</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -2136,76 +2136,76 @@
         <v>80</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10.41</v>
+        <v>6.1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43.17</v>
+        <v>47.84</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3053</v>
+        <v>-0.0107</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.1574</v>
+        <v>0.0032</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.378</v>
+        <v>0.031</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>2.91</v>
+        <v>3.56</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>30.77</v>
+        <v>30.22</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>95.64</v>
+        <v>51.52</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>96.08</v>
+        <v>46.08</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-4.75</v>
+        <v>-20.93</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-11.31</v>
+        <v>-21.65</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>6.57</v>
+        <v>0.72</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-43.41</v>
+        <v>-3.73</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-68.65000000000001</v>
+        <v>-14.64</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>13.03</v>
+        <v>0.86</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>12.99</v>
+        <v>0.86</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>12.98</v>
+        <v>0.87</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>13.12</v>
+        <v>0.87</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>13.58</v>
+        <v>0.89</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>14.49</v>
+        <v>0.91</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
@@ -2225,143 +2225,147 @@
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>1.8684</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>103526167</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>130019425</v>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
           <t>2/5</t>
-        </is>
-      </c>
-      <c r="AG6" s="3" t="n">
-        <v>19.505</v>
-      </c>
-      <c r="AH6" s="3" t="n">
-        <v>-33.4</v>
-      </c>
-      <c r="AI6" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>6194991</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>9330204</v>
-      </c>
-      <c r="AL6" s="3" t="inlineStr">
-        <is>
-          <t>1/5</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21-08-26</t>
+      <c r="AP6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27-08-26</t>
+      <c r="AR6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr"/>
       <c r="AT6" s="8" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr"/>
       <c r="AV6" s="8" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 16-04-26</t>
-        </is>
-      </c>
-      <c r="AY6" s="8" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BB6" s="3" t="inlineStr"/>
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr"/>
       <c r="BG6" s="3" t="n">
-        <v>13.06</v>
+        <v>0.87</v>
       </c>
       <c r="BH6" s="3" t="n">
-        <v>13.15</v>
+        <v>0.89</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>13.3</v>
+        <v>0.91</v>
       </c>
       <c r="BJ6" s="3" t="n">
-        <v>13.39</v>
+        <v>0.93</v>
       </c>
       <c r="BK6" s="3" t="n">
-        <v>12.91</v>
+        <v>0.85</v>
       </c>
       <c r="BL6" s="3" t="n">
-        <v>12.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" s="3" t="n">
-        <v>12.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" s="3" t="n">
-        <v>13.08</v>
+        <v>0.87</v>
       </c>
       <c r="BO6" s="3" t="n">
-        <v>13.27</v>
+        <v>0.89</v>
       </c>
       <c r="BP6" s="3" t="n">
-        <v>13.54</v>
+        <v>0.91</v>
       </c>
       <c r="BQ6" s="3" t="n">
-        <v>13.73</v>
+        <v>0.93</v>
       </c>
       <c r="BR6" s="3" t="n">
-        <v>12.81</v>
+        <v>0.85</v>
       </c>
       <c r="BS6" s="3" t="n">
-        <v>12.62</v>
+        <v>0.83</v>
       </c>
       <c r="BT6" s="3" t="n">
-        <v>12.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BU6" s="3" t="n">
-        <v>12.95</v>
+        <v>0.87</v>
       </c>
       <c r="BV6" s="3" t="n">
-        <v>13.55</v>
+        <v>0.92</v>
       </c>
       <c r="BW6" s="3" t="n">
-        <v>14.12</v>
+        <v>0.96</v>
       </c>
       <c r="BX6" s="3" t="n">
-        <v>14.72</v>
+        <v>1.01</v>
       </c>
       <c r="BY6" s="3" t="n">
-        <v>12.38</v>
+        <v>0.83</v>
       </c>
       <c r="BZ6" s="3" t="n">
-        <v>11.78</v>
+        <v>0.78</v>
       </c>
       <c r="CA6" s="3" t="n">
-        <v>11.21</v>
+        <v>0.74</v>
       </c>
       <c r="CB6" s="8" t="inlineStr">
         <is>
@@ -2370,24 +2374,24 @@
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>T6 21-08-26 @13.42</t>
+          <t>T23 23-07-26 @0.95</t>
         </is>
       </c>
       <c r="CD6" s="3" t="inlineStr">
         <is>
-          <t>D8 11-08-26 @12.34</t>
+          <t>D24 11-08-26 @0.83</t>
         </is>
       </c>
       <c r="CE6" s="3" t="inlineStr">
         <is>
-          <t>19-08-26</t>
+          <t>17-08-26</t>
         </is>
       </c>
       <c r="CF6" s="3" t="n">
-        <v>12.72</v>
+        <v>0.91</v>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CH6" s="3" t="inlineStr"/>
       <c r="CI6" s="3" t="inlineStr"/>
@@ -2395,14 +2399,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.87</v>
+        <v>12.99</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1.16</v>
+        <v>-1.07</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -2413,236 +2417,232 @@
         <v>80</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>6.1</v>
+        <v>10.41</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>47.84</v>
+        <v>43.17</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.3053</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.1574</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.031</v>
+        <v>0.378</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>3.56</v>
+        <v>2.91</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>30.22</v>
+        <v>30.77</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>51.52</v>
+        <v>95.64</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>46.08</v>
+        <v>96.08</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-20.93</v>
+        <v>-4.75</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>-21.65</v>
+        <v>-11.31</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>0.72</v>
+        <v>6.57</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-3.73</v>
+        <v>-43.41</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>-14.64</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>0.86</v>
+        <v>13.03</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0.86</v>
+        <v>12.99</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0.87</v>
+        <v>12.98</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0.87</v>
+        <v>13.12</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>0.89</v>
+        <v>13.58</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>0.91</v>
+        <v>14.49</v>
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AG7" s="5" t="n">
-        <v>1.8684</v>
+        <v>19.505</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>-53.44</v>
+        <v>-33.4</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>103526167</v>
+        <v>6194991</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>130019425</v>
+        <v>9330204</v>
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr"/>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr"/>
-      <c r="AP7" s="7" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AP7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AQ7" s="5" t="inlineStr"/>
-      <c r="AR7" s="7" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AR7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
         </is>
       </c>
       <c r="AS7" s="5" t="inlineStr"/>
       <c r="AT7" s="7" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AU7" s="5" t="inlineStr"/>
       <c r="AV7" s="7" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AW7" s="5" t="inlineStr"/>
-      <c r="AX7" s="5" t="inlineStr"/>
-      <c r="AY7" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="AZ7" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="BA7" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="AX7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 16-04-26</t>
+        </is>
+      </c>
+      <c r="AY7" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ7" s="5" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
       <c r="BB7" s="5" t="inlineStr"/>
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
-      <c r="BE7" s="5" t="inlineStr">
-        <is>
-          <t>5-8-13</t>
-        </is>
-      </c>
-      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BE7" s="5" t="inlineStr"/>
+      <c r="BF7" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="BG7" s="5" t="n">
-        <v>0.87</v>
+        <v>13.06</v>
       </c>
       <c r="BH7" s="5" t="n">
-        <v>0.89</v>
+        <v>13.15</v>
       </c>
       <c r="BI7" s="5" t="n">
-        <v>0.91</v>
+        <v>13.3</v>
       </c>
       <c r="BJ7" s="5" t="n">
-        <v>0.93</v>
+        <v>13.39</v>
       </c>
       <c r="BK7" s="5" t="n">
-        <v>0.85</v>
+        <v>12.91</v>
       </c>
       <c r="BL7" s="5" t="n">
-        <v>0.83</v>
+        <v>12.82</v>
       </c>
       <c r="BM7" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.67</v>
       </c>
       <c r="BN7" s="5" t="n">
-        <v>0.87</v>
+        <v>13.08</v>
       </c>
       <c r="BO7" s="5" t="n">
-        <v>0.89</v>
+        <v>13.27</v>
       </c>
       <c r="BP7" s="5" t="n">
-        <v>0.91</v>
+        <v>13.54</v>
       </c>
       <c r="BQ7" s="5" t="n">
-        <v>0.93</v>
+        <v>13.73</v>
       </c>
       <c r="BR7" s="5" t="n">
-        <v>0.85</v>
+        <v>12.81</v>
       </c>
       <c r="BS7" s="5" t="n">
-        <v>0.83</v>
+        <v>12.62</v>
       </c>
       <c r="BT7" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.35</v>
       </c>
       <c r="BU7" s="5" t="n">
-        <v>0.87</v>
+        <v>12.95</v>
       </c>
       <c r="BV7" s="5" t="n">
-        <v>0.92</v>
+        <v>13.55</v>
       </c>
       <c r="BW7" s="5" t="n">
-        <v>0.96</v>
+        <v>14.12</v>
       </c>
       <c r="BX7" s="5" t="n">
-        <v>1.01</v>
+        <v>14.72</v>
       </c>
       <c r="BY7" s="5" t="n">
-        <v>0.83</v>
+        <v>12.38</v>
       </c>
       <c r="BZ7" s="5" t="n">
-        <v>0.78</v>
+        <v>11.78</v>
       </c>
       <c r="CA7" s="5" t="n">
-        <v>0.74</v>
+        <v>11.21</v>
       </c>
       <c r="CB7" s="7" t="inlineStr">
         <is>
@@ -2651,24 +2651,24 @@
       </c>
       <c r="CC7" s="5" t="inlineStr">
         <is>
-          <t>T23 23-07-26 @0.95</t>
+          <t>T6 21-08-26 @13.42</t>
         </is>
       </c>
       <c r="CD7" s="5" t="inlineStr">
         <is>
-          <t>D24 11-08-26 @0.83</t>
+          <t>D8 11-08-26 @12.34</t>
         </is>
       </c>
       <c r="CE7" s="5" t="inlineStr">
         <is>
-          <t>17-08-26</t>
+          <t>19-08-26</t>
         </is>
       </c>
       <c r="CF7" s="5" t="n">
-        <v>0.91</v>
+        <v>12.72</v>
       </c>
       <c r="CG7" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CH7" s="5" t="inlineStr"/>
       <c r="CI7" s="5" t="inlineStr"/>
@@ -3865,7 +3865,7 @@
     <col width="16" customWidth="1" min="84" max="84"/>
     <col width="20" customWidth="1" min="85" max="85"/>
     <col width="13" customWidth="1" min="86" max="86"/>
-    <col width="8" customWidth="1" min="87" max="87"/>
+    <col width="18" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4858,14 +4858,14 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>35.44</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.86</v>
+        <v>1.72</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -4876,67 +4876,67 @@
         <v>94</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7.98</v>
+        <v>23.15</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>47.78</v>
+        <v>61.33</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-0.2832</v>
+        <v>1.2997</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.099</v>
+        <v>0.3751</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>7.73</v>
+        <v>6.94</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.2781</v>
+        <v>1.7785</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>3.22</v>
+        <v>5.02</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>22.59</v>
+        <v>37.93</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>98.43000000000001</v>
+        <v>39.34</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>86.15000000000001</v>
+        <v>65.17</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>-24.38</v>
+        <v>52.35</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>-36.54</v>
+        <v>53.21</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>12.15</v>
+        <v>-0.86</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>-287.49</v>
+        <v>151.57</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>-363.06</v>
+        <v>149.19</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>8.44</v>
+        <v>35.39</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>8.4</v>
+        <v>34.96</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>8.42</v>
+        <v>34.22</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>8.57</v>
+        <v>33.37</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>8.9</v>
+        <v>32.81</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.460000000000001</v>
+        <v>32.91</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -4945,47 +4945,47 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>11.1687</v>
+        <v>37.0379</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-22.64</v>
+        <v>-4.31</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>0.87</v>
+        <v>2.86</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>6736736</v>
+        <v>10999396</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>7700768</v>
+        <v>3843601</v>
       </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -4995,162 +4995,158 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
+          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="4" t="inlineStr">
         <is>
-          <t>▲ 26-08-26</t>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="8" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="8" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AT4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 12-08-26</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="8" t="inlineStr">
-        <is>
-          <t>▼ 27-03-26</t>
+      <c r="AV4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20-08-26</t>
         </is>
       </c>
       <c r="AW4" s="3" t="inlineStr"/>
       <c r="AX4" s="8" t="inlineStr">
         <is>
-          <t>▼ 24-04-26</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr"/>
+          <t>▼ 02-06-26</t>
+        </is>
+      </c>
+      <c r="AY4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="AZ4" s="3" t="inlineStr"/>
       <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="BB4" s="3" t="inlineStr"/>
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BF4" s="3" t="inlineStr"/>
       <c r="BG4" s="3" t="n">
-        <v>8.550000000000001</v>
+        <v>35.57</v>
       </c>
       <c r="BH4" s="3" t="n">
-        <v>8.73</v>
+        <v>36.27</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>8.81</v>
+        <v>37.11</v>
       </c>
       <c r="BJ4" s="3" t="n">
-        <v>8.99</v>
+        <v>37.81</v>
       </c>
       <c r="BK4" s="3" t="n">
-        <v>8.470000000000001</v>
+        <v>34.73</v>
       </c>
       <c r="BL4" s="3" t="n">
-        <v>8.289999999999999</v>
+        <v>34.03</v>
       </c>
       <c r="BM4" s="3" t="n">
-        <v>8.210000000000001</v>
+        <v>33.19</v>
       </c>
       <c r="BN4" s="3" t="n">
-        <v>8.49</v>
+        <v>36.03</v>
       </c>
       <c r="BO4" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>38.51</v>
       </c>
       <c r="BP4" s="3" t="n">
-        <v>8.94</v>
+        <v>41.57</v>
       </c>
       <c r="BQ4" s="3" t="n">
-        <v>9.24</v>
+        <v>44.05</v>
       </c>
       <c r="BR4" s="3" t="n">
-        <v>8.34</v>
+        <v>32.97</v>
       </c>
       <c r="BS4" s="3" t="n">
-        <v>8.039999999999999</v>
+        <v>30.49</v>
       </c>
       <c r="BT4" s="3" t="n">
-        <v>7.89</v>
+        <v>27.43</v>
       </c>
       <c r="BU4" s="3" t="n">
-        <v>8.66</v>
+        <v>34.31</v>
       </c>
       <c r="BV4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>40.23</v>
       </c>
       <c r="BW4" s="3" t="n">
-        <v>9.960000000000001</v>
+        <v>45.01</v>
       </c>
       <c r="BX4" s="3" t="n">
-        <v>10.6</v>
+        <v>50.93</v>
       </c>
       <c r="BY4" s="3" t="n">
-        <v>8</v>
+        <v>29.53</v>
       </c>
       <c r="BZ4" s="3" t="n">
-        <v>7.36</v>
+        <v>23.61</v>
       </c>
       <c r="CA4" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="CB4" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
+        <v>18.83</v>
+      </c>
+      <c r="CB4" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="CC4" s="3" t="inlineStr">
         <is>
-          <t>T26 18-08-26 @8.45</t>
+          <t>T31 25-08-26 @39.1</t>
         </is>
       </c>
       <c r="CD4" s="3" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @8.58</t>
+          <t>D28 31-07-26 @28.4</t>
         </is>
       </c>
       <c r="CE4" s="3" t="inlineStr">
         <is>
-          <t>26-08-26</t>
+          <t>07-08-26</t>
         </is>
       </c>
       <c r="CF4" s="3" t="n">
-        <v>8.43</v>
+        <v>32.42</v>
       </c>
       <c r="CG4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="CH4" s="3" t="inlineStr">
-        <is>
-          <t>26-08-26</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="CH4" s="3" t="inlineStr"/>
       <c r="CI4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>A1CAP</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>35.44</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1.72</v>
+        <v>2.86</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -5161,67 +5157,67 @@
         <v>94</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>23.15</v>
+        <v>7.98</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>61.33</v>
+        <v>47.78</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1.2997</v>
+        <v>-0.2832</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.3751</v>
+        <v>0.099</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>6.94</v>
+        <v>7.73</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1.7785</v>
+        <v>0.2781</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>5.02</v>
+        <v>3.22</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>37.93</v>
+        <v>22.59</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>39.34</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>65.17</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>52.35</v>
+        <v>-24.38</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>53.21</v>
+        <v>-36.54</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>-0.86</v>
+        <v>12.15</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>151.57</v>
+        <v>-287.49</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>149.19</v>
+        <v>-363.06</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>35.39</v>
+        <v>8.44</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>34.96</v>
+        <v>8.4</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>34.22</v>
+        <v>8.42</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>33.37</v>
+        <v>8.57</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>32.81</v>
+        <v>8.9</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>32.91</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AA5" s="5" t="inlineStr">
         <is>
@@ -5230,17 +5226,17 @@
       </c>
       <c r="AB5" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC5" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD5" s="5" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AE5" s="5" t="inlineStr">
@@ -5250,27 +5246,27 @@
       </c>
       <c r="AF5" s="5" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>37.0379</v>
+        <v>11.1687</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>-4.31</v>
+        <v>-22.64</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>2.86</v>
+        <v>0.87</v>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>10999396</v>
+        <v>6736736</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>3843601</v>
+        <v>7700768</v>
       </c>
       <c r="AL5" s="5" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="AM5" s="5" t="inlineStr">
@@ -5280,158 +5276,162 @@
       </c>
       <c r="AN5" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
         </is>
       </c>
       <c r="AO5" s="5" t="inlineStr"/>
       <c r="AP5" s="6" t="inlineStr">
         <is>
-          <t>▲ 07-08-26</t>
+          <t>▲ 26-08-26</t>
         </is>
       </c>
       <c r="AQ5" s="5" t="inlineStr"/>
-      <c r="AR5" s="6" t="inlineStr">
-        <is>
-          <t>▲ 07-08-26</t>
+      <c r="AR5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AS5" s="5" t="inlineStr"/>
-      <c r="AT5" s="6" t="inlineStr">
-        <is>
-          <t>▲ 12-08-26</t>
+      <c r="AT5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AU5" s="5" t="inlineStr"/>
-      <c r="AV5" s="6" t="inlineStr">
-        <is>
-          <t>▲ 20-08-26</t>
+      <c r="AV5" s="7" t="inlineStr">
+        <is>
+          <t>▼ 27-03-26</t>
         </is>
       </c>
       <c r="AW5" s="5" t="inlineStr"/>
       <c r="AX5" s="7" t="inlineStr">
         <is>
-          <t>▼ 02-06-26</t>
-        </is>
-      </c>
-      <c r="AY5" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+          <t>▼ 24-04-26</t>
+        </is>
+      </c>
+      <c r="AY5" s="5" t="inlineStr"/>
       <c r="AZ5" s="5" t="inlineStr"/>
       <c r="BA5" s="5" t="inlineStr"/>
-      <c r="BB5" s="5" t="inlineStr"/>
+      <c r="BB5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BF5" s="5" t="inlineStr"/>
       <c r="BG5" s="5" t="n">
-        <v>35.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BH5" s="5" t="n">
-        <v>36.27</v>
+        <v>8.73</v>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>37.11</v>
+        <v>8.81</v>
       </c>
       <c r="BJ5" s="5" t="n">
-        <v>37.81</v>
+        <v>8.99</v>
       </c>
       <c r="BK5" s="5" t="n">
-        <v>34.73</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BL5" s="5" t="n">
-        <v>34.03</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BM5" s="5" t="n">
-        <v>33.19</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BN5" s="5" t="n">
-        <v>36.03</v>
+        <v>8.49</v>
       </c>
       <c r="BO5" s="5" t="n">
-        <v>38.51</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BP5" s="5" t="n">
-        <v>41.57</v>
+        <v>8.94</v>
       </c>
       <c r="BQ5" s="5" t="n">
-        <v>44.05</v>
+        <v>9.24</v>
       </c>
       <c r="BR5" s="5" t="n">
-        <v>32.97</v>
+        <v>8.34</v>
       </c>
       <c r="BS5" s="5" t="n">
-        <v>30.49</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BT5" s="5" t="n">
-        <v>27.43</v>
+        <v>7.89</v>
       </c>
       <c r="BU5" s="5" t="n">
-        <v>34.31</v>
+        <v>8.66</v>
       </c>
       <c r="BV5" s="5" t="n">
-        <v>40.23</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BW5" s="5" t="n">
-        <v>45.01</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BX5" s="5" t="n">
-        <v>50.93</v>
+        <v>10.6</v>
       </c>
       <c r="BY5" s="5" t="n">
-        <v>29.53</v>
+        <v>8</v>
       </c>
       <c r="BZ5" s="5" t="n">
-        <v>23.61</v>
+        <v>7.36</v>
       </c>
       <c r="CA5" s="5" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="CB5" s="7" t="inlineStr">
-        <is>
-          <t>▼</t>
+        <v>6.7</v>
+      </c>
+      <c r="CB5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
         </is>
       </c>
       <c r="CC5" s="5" t="inlineStr">
         <is>
-          <t>T31 25-08-26 @39.1</t>
+          <t>T26 18-08-26 @8.45</t>
         </is>
       </c>
       <c r="CD5" s="5" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @28.4</t>
+          <t>D28 31-07-26 @8.58</t>
         </is>
       </c>
       <c r="CE5" s="5" t="inlineStr">
         <is>
-          <t>07-08-26</t>
+          <t>26-08-26</t>
         </is>
       </c>
       <c r="CF5" s="5" t="n">
-        <v>32.42</v>
+        <v>8.43</v>
       </c>
       <c r="CG5" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="CH5" s="5" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="CH5" s="5" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
       <c r="CI5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12.99</v>
+        <v>0.87</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>-1.07</v>
+        <v>1.16</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -5442,76 +5442,76 @@
         <v>80</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10.41</v>
+        <v>6.1</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43.17</v>
+        <v>47.84</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.3053</v>
+        <v>-0.0107</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.1574</v>
+        <v>0.0032</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.48</v>
+        <v>1.16</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.378</v>
+        <v>0.031</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>2.91</v>
+        <v>3.56</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>30.77</v>
+        <v>30.22</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>95.64</v>
+        <v>51.52</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>96.08</v>
+        <v>46.08</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-4.75</v>
+        <v>-20.93</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-11.31</v>
+        <v>-21.65</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>6.57</v>
+        <v>0.72</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-43.41</v>
+        <v>-3.73</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-68.65000000000001</v>
+        <v>-14.64</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>13.03</v>
+        <v>0.86</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>12.99</v>
+        <v>0.86</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>12.98</v>
+        <v>0.87</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>13.12</v>
+        <v>0.87</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>13.58</v>
+        <v>0.89</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>14.49</v>
+        <v>0.91</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
@@ -5531,143 +5531,147 @@
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>1.8684</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-53.44</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>103526167</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>130019425</v>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
           <t>2/5</t>
-        </is>
-      </c>
-      <c r="AG6" s="3" t="n">
-        <v>19.505</v>
-      </c>
-      <c r="AH6" s="3" t="n">
-        <v>-33.4</v>
-      </c>
-      <c r="AI6" s="3" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>6194991</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>9330204</v>
-      </c>
-      <c r="AL6" s="3" t="inlineStr">
-        <is>
-          <t>1/5</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 21-08-26</t>
+      <c r="AP6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 27-08-26</t>
+      <c r="AR6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr"/>
       <c r="AT6" s="8" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr"/>
       <c r="AV6" s="8" t="inlineStr">
         <is>
-          <t>▼ 15-04-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 16-04-26</t>
-        </is>
-      </c>
-      <c r="AY6" s="8" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA6" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BB6" s="3" t="inlineStr"/>
       <c r="BC6" s="3" t="inlineStr"/>
       <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr"/>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr"/>
       <c r="BG6" s="3" t="n">
-        <v>13.06</v>
+        <v>0.87</v>
       </c>
       <c r="BH6" s="3" t="n">
-        <v>13.15</v>
+        <v>0.89</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>13.3</v>
+        <v>0.91</v>
       </c>
       <c r="BJ6" s="3" t="n">
-        <v>13.39</v>
+        <v>0.93</v>
       </c>
       <c r="BK6" s="3" t="n">
-        <v>12.91</v>
+        <v>0.85</v>
       </c>
       <c r="BL6" s="3" t="n">
-        <v>12.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" s="3" t="n">
-        <v>12.67</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" s="3" t="n">
-        <v>13.08</v>
+        <v>0.87</v>
       </c>
       <c r="BO6" s="3" t="n">
-        <v>13.27</v>
+        <v>0.89</v>
       </c>
       <c r="BP6" s="3" t="n">
-        <v>13.54</v>
+        <v>0.91</v>
       </c>
       <c r="BQ6" s="3" t="n">
-        <v>13.73</v>
+        <v>0.93</v>
       </c>
       <c r="BR6" s="3" t="n">
-        <v>12.81</v>
+        <v>0.85</v>
       </c>
       <c r="BS6" s="3" t="n">
-        <v>12.62</v>
+        <v>0.83</v>
       </c>
       <c r="BT6" s="3" t="n">
-        <v>12.35</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BU6" s="3" t="n">
-        <v>12.95</v>
+        <v>0.87</v>
       </c>
       <c r="BV6" s="3" t="n">
-        <v>13.55</v>
+        <v>0.92</v>
       </c>
       <c r="BW6" s="3" t="n">
-        <v>14.12</v>
+        <v>0.96</v>
       </c>
       <c r="BX6" s="3" t="n">
-        <v>14.72</v>
+        <v>1.01</v>
       </c>
       <c r="BY6" s="3" t="n">
-        <v>12.38</v>
+        <v>0.83</v>
       </c>
       <c r="BZ6" s="3" t="n">
-        <v>11.78</v>
+        <v>0.78</v>
       </c>
       <c r="CA6" s="3" t="n">
-        <v>11.21</v>
+        <v>0.74</v>
       </c>
       <c r="CB6" s="8" t="inlineStr">
         <is>
@@ -5676,24 +5680,24 @@
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>T6 21-08-26 @13.42</t>
+          <t>T23 23-07-26 @0.95</t>
         </is>
       </c>
       <c r="CD6" s="3" t="inlineStr">
         <is>
-          <t>D8 11-08-26 @12.34</t>
+          <t>D24 11-08-26 @0.83</t>
         </is>
       </c>
       <c r="CE6" s="3" t="inlineStr">
         <is>
-          <t>19-08-26</t>
+          <t>17-08-26</t>
         </is>
       </c>
       <c r="CF6" s="3" t="n">
-        <v>12.72</v>
+        <v>0.91</v>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CH6" s="3" t="inlineStr"/>
       <c r="CI6" s="3" t="inlineStr"/>
@@ -5701,14 +5705,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.87</v>
+        <v>12.99</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1.16</v>
+        <v>-1.07</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -5719,236 +5723,232 @@
         <v>80</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>6.1</v>
+        <v>10.41</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>47.84</v>
+        <v>43.17</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.3053</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.1574</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1.16</v>
+        <v>1.48</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.031</v>
+        <v>0.378</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>3.56</v>
+        <v>2.91</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>30.22</v>
+        <v>30.77</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>51.52</v>
+        <v>95.64</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>46.08</v>
+        <v>96.08</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-20.93</v>
+        <v>-4.75</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>-21.65</v>
+        <v>-11.31</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>0.72</v>
+        <v>6.57</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>-3.73</v>
+        <v>-43.41</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>-14.64</v>
+        <v>-68.65000000000001</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>0.86</v>
+        <v>13.03</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0.86</v>
+        <v>12.99</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0.87</v>
+        <v>12.98</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0.87</v>
+        <v>13.12</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>0.89</v>
+        <v>13.58</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>0.91</v>
+        <v>14.49</v>
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC7" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE7" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
-          <t>0/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AG7" s="5" t="n">
-        <v>1.8684</v>
+        <v>19.505</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>-53.44</v>
+        <v>-33.4</v>
       </c>
       <c r="AI7" s="5" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>103526167</v>
+        <v>6194991</v>
       </c>
       <c r="AK7" s="5" t="n">
-        <v>130019425</v>
+        <v>9330204</v>
       </c>
       <c r="AL7" s="5" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AM7" s="5" t="inlineStr"/>
       <c r="AN7" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 19-08-26 tarihinde düşen trend (15-06-26–16-07-26, ~%14.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO7" s="5" t="inlineStr"/>
-      <c r="AP7" s="7" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AP7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AQ7" s="5" t="inlineStr"/>
-      <c r="AR7" s="7" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AR7" s="6" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
         </is>
       </c>
       <c r="AS7" s="5" t="inlineStr"/>
       <c r="AT7" s="7" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AU7" s="5" t="inlineStr"/>
       <c r="AV7" s="7" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 15-04-26</t>
         </is>
       </c>
       <c r="AW7" s="5" t="inlineStr"/>
-      <c r="AX7" s="5" t="inlineStr"/>
-      <c r="AY7" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="AZ7" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="BA7" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="AX7" s="7" t="inlineStr">
+        <is>
+          <t>▼ 16-04-26</t>
+        </is>
+      </c>
+      <c r="AY7" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ7" s="5" t="inlineStr"/>
+      <c r="BA7" s="5" t="inlineStr"/>
       <c r="BB7" s="5" t="inlineStr"/>
       <c r="BC7" s="5" t="inlineStr"/>
       <c r="BD7" s="5" t="inlineStr"/>
-      <c r="BE7" s="5" t="inlineStr">
-        <is>
-          <t>5-8-13</t>
-        </is>
-      </c>
-      <c r="BF7" s="5" t="inlineStr"/>
+      <c r="BE7" s="5" t="inlineStr"/>
+      <c r="BF7" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="BG7" s="5" t="n">
-        <v>0.87</v>
+        <v>13.06</v>
       </c>
       <c r="BH7" s="5" t="n">
-        <v>0.89</v>
+        <v>13.15</v>
       </c>
       <c r="BI7" s="5" t="n">
-        <v>0.91</v>
+        <v>13.3</v>
       </c>
       <c r="BJ7" s="5" t="n">
-        <v>0.93</v>
+        <v>13.39</v>
       </c>
       <c r="BK7" s="5" t="n">
-        <v>0.85</v>
+        <v>12.91</v>
       </c>
       <c r="BL7" s="5" t="n">
-        <v>0.83</v>
+        <v>12.82</v>
       </c>
       <c r="BM7" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.67</v>
       </c>
       <c r="BN7" s="5" t="n">
-        <v>0.87</v>
+        <v>13.08</v>
       </c>
       <c r="BO7" s="5" t="n">
-        <v>0.89</v>
+        <v>13.27</v>
       </c>
       <c r="BP7" s="5" t="n">
-        <v>0.91</v>
+        <v>13.54</v>
       </c>
       <c r="BQ7" s="5" t="n">
-        <v>0.93</v>
+        <v>13.73</v>
       </c>
       <c r="BR7" s="5" t="n">
-        <v>0.85</v>
+        <v>12.81</v>
       </c>
       <c r="BS7" s="5" t="n">
-        <v>0.83</v>
+        <v>12.62</v>
       </c>
       <c r="BT7" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.35</v>
       </c>
       <c r="BU7" s="5" t="n">
-        <v>0.87</v>
+        <v>12.95</v>
       </c>
       <c r="BV7" s="5" t="n">
-        <v>0.92</v>
+        <v>13.55</v>
       </c>
       <c r="BW7" s="5" t="n">
-        <v>0.96</v>
+        <v>14.12</v>
       </c>
       <c r="BX7" s="5" t="n">
-        <v>1.01</v>
+        <v>14.72</v>
       </c>
       <c r="BY7" s="5" t="n">
-        <v>0.83</v>
+        <v>12.38</v>
       </c>
       <c r="BZ7" s="5" t="n">
-        <v>0.78</v>
+        <v>11.78</v>
       </c>
       <c r="CA7" s="5" t="n">
-        <v>0.74</v>
+        <v>11.21</v>
       </c>
       <c r="CB7" s="7" t="inlineStr">
         <is>
@@ -5957,24 +5957,24 @@
       </c>
       <c r="CC7" s="5" t="inlineStr">
         <is>
-          <t>T23 23-07-26 @0.95</t>
+          <t>T6 21-08-26 @13.42</t>
         </is>
       </c>
       <c r="CD7" s="5" t="inlineStr">
         <is>
-          <t>D24 11-08-26 @0.83</t>
+          <t>D8 11-08-26 @12.34</t>
         </is>
       </c>
       <c r="CE7" s="5" t="inlineStr">
         <is>
-          <t>17-08-26</t>
+          <t>19-08-26</t>
         </is>
       </c>
       <c r="CF7" s="5" t="n">
-        <v>0.91</v>
+        <v>12.72</v>
       </c>
       <c r="CG7" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CH7" s="5" t="inlineStr"/>
       <c r="CI7" s="5" t="inlineStr"/>
@@ -6532,7 +6532,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>AFYON</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr"/>
@@ -6626,14 +6626,14 @@
       <c r="CH10" s="3" t="inlineStr"/>
       <c r="CI10" s="3" t="inlineStr">
         <is>
-          <t>'kind'</t>
+          <t>KeyError: 'kind'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>AFYON</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
@@ -6727,7 +6727,7 @@
       <c r="CH11" s="5" t="inlineStr"/>
       <c r="CI11" s="5" t="inlineStr">
         <is>
-          <t>'kind'</t>
+          <t>KeyError: 'kind'</t>
         </is>
       </c>
     </row>

--- a/ObvTarama_Gunluk_28082026_06:00.xlsx
+++ b/ObvTarama_Gunluk_28082026_06:00.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TUMU" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KIRILIMLAR'!$A$1:$CI$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'YAKLASANLAR'!$A$1:$CI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUMU'!$A$1:$CI$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'KIRILIMLAR'!$A$1:$CH$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'YAKLASANLAR'!$A$1:$CH$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'TUMU'!$A$1:$CH$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI9"/>
+  <dimension ref="A1:CH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <col width="8" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
     <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="7" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
     <col width="5" customWidth="1" min="27" max="27"/>
     <col width="6" customWidth="1" min="28" max="28"/>
     <col width="7" customWidth="1" min="29" max="29"/>
@@ -559,7 +559,6 @@
     <col width="16" customWidth="1" min="84" max="84"/>
     <col width="20" customWidth="1" min="85" max="85"/>
     <col width="13" customWidth="1" min="86" max="86"/>
-    <col width="6" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -991,11 +990,6 @@
       <c r="CH1" s="2" t="inlineStr">
         <is>
           <t>OBV kırılım</t>
-        </is>
-      </c>
-      <c r="CI1" s="2" t="inlineStr">
-        <is>
-          <t>Hata</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1264,6 @@
           <t>21-08-26</t>
         </is>
       </c>
-      <c r="CI2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1547,19 +1540,18 @@
           <t>14-08-26</t>
         </is>
       </c>
-      <c r="CI3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>A1CAP</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>35.44</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1.72</v>
+        <v>2.86</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -1570,67 +1562,67 @@
         <v>94</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23.15</v>
+        <v>7.98</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>61.33</v>
+        <v>47.78</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1.2997</v>
+        <v>-0.2832</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3751</v>
+        <v>0.099</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>6.94</v>
+        <v>7.73</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.7785</v>
+        <v>0.2781</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5.02</v>
+        <v>3.22</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>37.93</v>
+        <v>22.59</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>39.34</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>65.17</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>52.35</v>
+        <v>-24.38</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>53.21</v>
+        <v>-36.54</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-0.86</v>
+        <v>12.15</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>151.57</v>
+        <v>-287.49</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>149.19</v>
+        <v>-363.06</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>35.39</v>
+        <v>8.44</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>34.96</v>
+        <v>8.4</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>34.22</v>
+        <v>8.42</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>33.37</v>
+        <v>8.57</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>32.81</v>
+        <v>8.9</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.91</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -1639,17 +1631,17 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
@@ -1659,27 +1651,27 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>37.0379</v>
+        <v>11.1687</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-4.31</v>
+        <v>-22.64</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>2.86</v>
+        <v>0.87</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>10999396</v>
+        <v>6736736</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>3843601</v>
+        <v>7700768</v>
       </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1689,158 +1681,161 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="4" t="inlineStr">
         <is>
-          <t>▲ 07-08-26</t>
+          <t>▲ 26-08-26</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 07-08-26</t>
+      <c r="AR4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12-08-26</t>
+      <c r="AT4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20-08-26</t>
+      <c r="AV4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 27-03-26</t>
         </is>
       </c>
       <c r="AW4" s="3" t="inlineStr"/>
       <c r="AX4" s="8" t="inlineStr">
         <is>
-          <t>▼ 02-06-26</t>
-        </is>
-      </c>
-      <c r="AY4" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+          <t>▼ 24-04-26</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr"/>
       <c r="AZ4" s="3" t="inlineStr"/>
       <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BF4" s="3" t="inlineStr"/>
       <c r="BG4" s="3" t="n">
-        <v>35.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BH4" s="3" t="n">
-        <v>36.27</v>
+        <v>8.73</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>37.11</v>
+        <v>8.81</v>
       </c>
       <c r="BJ4" s="3" t="n">
-        <v>37.81</v>
+        <v>8.99</v>
       </c>
       <c r="BK4" s="3" t="n">
-        <v>34.73</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BL4" s="3" t="n">
-        <v>34.03</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BM4" s="3" t="n">
-        <v>33.19</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BN4" s="3" t="n">
-        <v>36.03</v>
+        <v>8.49</v>
       </c>
       <c r="BO4" s="3" t="n">
-        <v>38.51</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BP4" s="3" t="n">
-        <v>41.57</v>
+        <v>8.94</v>
       </c>
       <c r="BQ4" s="3" t="n">
-        <v>44.05</v>
+        <v>9.24</v>
       </c>
       <c r="BR4" s="3" t="n">
-        <v>32.97</v>
+        <v>8.34</v>
       </c>
       <c r="BS4" s="3" t="n">
-        <v>30.49</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BT4" s="3" t="n">
-        <v>27.43</v>
+        <v>7.89</v>
       </c>
       <c r="BU4" s="3" t="n">
-        <v>34.31</v>
+        <v>8.66</v>
       </c>
       <c r="BV4" s="3" t="n">
-        <v>40.23</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BW4" s="3" t="n">
-        <v>45.01</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BX4" s="3" t="n">
-        <v>50.93</v>
+        <v>10.6</v>
       </c>
       <c r="BY4" s="3" t="n">
-        <v>29.53</v>
+        <v>8</v>
       </c>
       <c r="BZ4" s="3" t="n">
-        <v>23.61</v>
+        <v>7.36</v>
       </c>
       <c r="CA4" s="3" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="CB4" s="8" t="inlineStr">
-        <is>
-          <t>▼</t>
+        <v>6.7</v>
+      </c>
+      <c r="CB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
         </is>
       </c>
       <c r="CC4" s="3" t="inlineStr">
         <is>
-          <t>T31 25-08-26 @39.1</t>
+          <t>T26 18-08-26 @8.45</t>
         </is>
       </c>
       <c r="CD4" s="3" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @28.4</t>
+          <t>D28 31-07-26 @8.58</t>
         </is>
       </c>
       <c r="CE4" s="3" t="inlineStr">
         <is>
-          <t>07-08-26</t>
+          <t>26-08-26</t>
         </is>
       </c>
       <c r="CF4" s="3" t="n">
-        <v>32.42</v>
+        <v>8.43</v>
       </c>
       <c r="CG4" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="CH4" s="3" t="inlineStr"/>
-      <c r="CI4" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="CH4" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>35.44</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2.86</v>
+        <v>1.72</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1851,67 +1846,67 @@
         <v>94</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>7.98</v>
+        <v>23.15</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>47.78</v>
+        <v>61.33</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.2832</v>
+        <v>1.2997</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.099</v>
+        <v>0.3751</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>7.73</v>
+        <v>6.94</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.2781</v>
+        <v>1.7785</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3.22</v>
+        <v>5.02</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>22.59</v>
+        <v>37.93</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>98.43000000000001</v>
+        <v>39.34</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>86.15000000000001</v>
+        <v>65.17</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-24.38</v>
+        <v>52.35</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>-36.54</v>
+        <v>53.21</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>12.15</v>
+        <v>-0.86</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-287.49</v>
+        <v>151.57</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>-363.06</v>
+        <v>149.19</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>8.44</v>
+        <v>35.39</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>8.4</v>
+        <v>34.96</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>8.42</v>
+        <v>34.22</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>8.57</v>
+        <v>33.37</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>8.9</v>
+        <v>32.81</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>9.460000000000001</v>
+        <v>32.91</v>
       </c>
       <c r="AA5" s="5" t="inlineStr">
         <is>
@@ -1920,47 +1915,47 @@
       </c>
       <c r="AB5" s="5" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE5" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF5" s="5" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>11.1687</v>
+        <v>37.0379</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>-22.64</v>
+        <v>-4.31</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>0.87</v>
+        <v>2.86</v>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>6736736</v>
+        <v>10999396</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>7700768</v>
+        <v>3843601</v>
       </c>
       <c r="AL5" s="5" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AM5" s="5" t="inlineStr">
@@ -1970,162 +1965,157 @@
       </c>
       <c r="AN5" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
+          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
         </is>
       </c>
       <c r="AO5" s="5" t="inlineStr"/>
       <c r="AP5" s="6" t="inlineStr">
         <is>
-          <t>▲ 26-08-26</t>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AQ5" s="5" t="inlineStr"/>
-      <c r="AR5" s="7" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AR5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AS5" s="5" t="inlineStr"/>
-      <c r="AT5" s="7" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AT5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 12-08-26</t>
         </is>
       </c>
       <c r="AU5" s="5" t="inlineStr"/>
-      <c r="AV5" s="7" t="inlineStr">
-        <is>
-          <t>▼ 27-03-26</t>
+      <c r="AV5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 20-08-26</t>
         </is>
       </c>
       <c r="AW5" s="5" t="inlineStr"/>
       <c r="AX5" s="7" t="inlineStr">
         <is>
-          <t>▼ 24-04-26</t>
-        </is>
-      </c>
-      <c r="AY5" s="5" t="inlineStr"/>
+          <t>▼ 02-06-26</t>
+        </is>
+      </c>
+      <c r="AY5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="AZ5" s="5" t="inlineStr"/>
       <c r="BA5" s="5" t="inlineStr"/>
-      <c r="BB5" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="BB5" s="5" t="inlineStr"/>
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BF5" s="5" t="inlineStr"/>
       <c r="BG5" s="5" t="n">
-        <v>8.550000000000001</v>
+        <v>35.57</v>
       </c>
       <c r="BH5" s="5" t="n">
-        <v>8.73</v>
+        <v>36.27</v>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>8.81</v>
+        <v>37.11</v>
       </c>
       <c r="BJ5" s="5" t="n">
-        <v>8.99</v>
+        <v>37.81</v>
       </c>
       <c r="BK5" s="5" t="n">
-        <v>8.470000000000001</v>
+        <v>34.73</v>
       </c>
       <c r="BL5" s="5" t="n">
-        <v>8.289999999999999</v>
+        <v>34.03</v>
       </c>
       <c r="BM5" s="5" t="n">
-        <v>8.210000000000001</v>
+        <v>33.19</v>
       </c>
       <c r="BN5" s="5" t="n">
-        <v>8.49</v>
+        <v>36.03</v>
       </c>
       <c r="BO5" s="5" t="n">
-        <v>8.789999999999999</v>
+        <v>38.51</v>
       </c>
       <c r="BP5" s="5" t="n">
-        <v>8.94</v>
+        <v>41.57</v>
       </c>
       <c r="BQ5" s="5" t="n">
-        <v>9.24</v>
+        <v>44.05</v>
       </c>
       <c r="BR5" s="5" t="n">
-        <v>8.34</v>
+        <v>32.97</v>
       </c>
       <c r="BS5" s="5" t="n">
-        <v>8.039999999999999</v>
+        <v>30.49</v>
       </c>
       <c r="BT5" s="5" t="n">
-        <v>7.89</v>
+        <v>27.43</v>
       </c>
       <c r="BU5" s="5" t="n">
-        <v>8.66</v>
+        <v>34.31</v>
       </c>
       <c r="BV5" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>40.23</v>
       </c>
       <c r="BW5" s="5" t="n">
-        <v>9.960000000000001</v>
+        <v>45.01</v>
       </c>
       <c r="BX5" s="5" t="n">
-        <v>10.6</v>
+        <v>50.93</v>
       </c>
       <c r="BY5" s="5" t="n">
-        <v>8</v>
+        <v>29.53</v>
       </c>
       <c r="BZ5" s="5" t="n">
-        <v>7.36</v>
+        <v>23.61</v>
       </c>
       <c r="CA5" s="5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="CB5" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
+        <v>18.83</v>
+      </c>
+      <c r="CB5" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="CC5" s="5" t="inlineStr">
         <is>
-          <t>T26 18-08-26 @8.45</t>
+          <t>T31 25-08-26 @39.1</t>
         </is>
       </c>
       <c r="CD5" s="5" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @8.58</t>
+          <t>D28 31-07-26 @28.4</t>
         </is>
       </c>
       <c r="CE5" s="5" t="inlineStr">
         <is>
-          <t>26-08-26</t>
+          <t>07-08-26</t>
         </is>
       </c>
       <c r="CF5" s="5" t="n">
-        <v>8.43</v>
+        <v>32.42</v>
       </c>
       <c r="CG5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CH5" s="5" t="inlineStr">
-        <is>
-          <t>26-08-26</t>
-        </is>
-      </c>
-      <c r="CI5" s="5" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="CH5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>AFYON</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.69</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.16</v>
+        <v>-0.08</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -2133,239 +2123,243 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6.1</v>
+        <v>1.71</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>47.84</v>
+        <v>50.78</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.0107</v>
+        <v>-0.0058</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.0382</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.031</v>
+        <v>0.3216</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.56</v>
+        <v>2.53</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>30.22</v>
+        <v>16.8</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>51.52</v>
+        <v>58.09</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>46.08</v>
+        <v>61.75</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-20.93</v>
+        <v>1.03</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-21.65</v>
+        <v>-2.32</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.72</v>
+        <v>3.35</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.73</v>
+        <v>12.78</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-14.64</v>
+        <v>-13.07</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.86</v>
+        <v>12.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.86</v>
+        <v>12.67</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.65</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.64</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.89</v>
+        <v>12.69</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.83</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>14.073</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-9.83</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>1998004</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>1569436</v>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
           <t>0/5</t>
         </is>
       </c>
-      <c r="AG6" s="3" t="n">
-        <v>1.8684</v>
-      </c>
-      <c r="AH6" s="3" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AI6" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>103526167</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>130019425</v>
-      </c>
-      <c r="AL6" s="3" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 21-08-26 tarihinde düşen trend (21-04-26–14-08-26, ~%12.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 21-08-26 tarihinde önceden kırmıştı.</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AR6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 21-05-26</t>
+      <c r="AT6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr"/>
       <c r="AV6" s="8" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 09-04-26</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="AZ6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="BA6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="AX6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 22-04-26</t>
+        </is>
+      </c>
+      <c r="AY6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
       <c r="BB6" s="3" t="inlineStr"/>
-      <c r="BC6" s="3" t="inlineStr"/>
+      <c r="BC6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
       <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>5-8-13</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>5-34</t>
+        </is>
+      </c>
       <c r="BG6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.73</v>
       </c>
       <c r="BH6" s="3" t="n">
-        <v>0.89</v>
+        <v>12.78</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.86</v>
       </c>
       <c r="BJ6" s="3" t="n">
-        <v>0.93</v>
+        <v>12.91</v>
       </c>
       <c r="BK6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.65</v>
       </c>
       <c r="BL6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.6</v>
       </c>
       <c r="BM6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="BN6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.91</v>
       </c>
       <c r="BO6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.17</v>
       </c>
       <c r="BP6" s="3" t="n">
-        <v>0.91</v>
+        <v>13.65</v>
       </c>
       <c r="BQ6" s="3" t="n">
-        <v>0.93</v>
+        <v>13.91</v>
       </c>
       <c r="BR6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.43</v>
       </c>
       <c r="BS6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.17</v>
       </c>
       <c r="BT6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>11.69</v>
       </c>
       <c r="BU6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.73</v>
       </c>
       <c r="BV6" s="3" t="n">
-        <v>0.92</v>
+        <v>13.35</v>
       </c>
       <c r="BW6" s="3" t="n">
-        <v>0.96</v>
+        <v>14</v>
       </c>
       <c r="BX6" s="3" t="n">
-        <v>1.01</v>
+        <v>14.62</v>
       </c>
       <c r="BY6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.08</v>
       </c>
       <c r="BZ6" s="3" t="n">
-        <v>0.78</v>
+        <v>11.46</v>
       </c>
       <c r="CA6" s="3" t="n">
-        <v>0.74</v>
+        <v>10.81</v>
       </c>
       <c r="CB6" s="8" t="inlineStr">
         <is>
@@ -2374,27 +2368,30 @@
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>T23 23-07-26 @0.95</t>
+          <t>T24 24-08-26 @13.39</t>
         </is>
       </c>
       <c r="CD6" s="3" t="inlineStr">
         <is>
-          <t>D24 11-08-26 @0.83</t>
+          <t>D29 18-08-26 @12.28</t>
         </is>
       </c>
       <c r="CE6" s="3" t="inlineStr">
         <is>
-          <t>17-08-26</t>
+          <t>21-08-26</t>
         </is>
       </c>
       <c r="CF6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.98</v>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="CH6" s="3" t="inlineStr"/>
-      <c r="CI6" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="CH6" s="3" t="inlineStr">
+        <is>
+          <t>21-08-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2671,7 +2668,6 @@
         <v>7</v>
       </c>
       <c r="CH7" s="5" t="inlineStr"/>
-      <c r="CI7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2948,90 +2944,89 @@
           <t>05-08-26</t>
         </is>
       </c>
-      <c r="CI8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>18.41</v>
+        <v>0.87</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.65</v>
+        <v>1.16</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Aşağı kırılım</t>
+          <t>Kırılım</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-2.1</v>
+        <v>6.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>31.61</v>
+        <v>47.84</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.0107</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0032</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-4.76</v>
+        <v>1.16</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.6009</v>
+        <v>0.031</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3.26</v>
+        <v>3.56</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>25.27</v>
+        <v>30.22</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>3.89</v>
+        <v>51.52</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>6.99</v>
+        <v>46.08</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>-44.67</v>
+        <v>-20.93</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>-41.73</v>
+        <v>-21.65</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>-2.94</v>
+        <v>0.72</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-133.9</v>
+        <v>-3.73</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>-131.16</v>
+        <v>-14.64</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>18.71</v>
+        <v>0.86</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>18.9</v>
+        <v>0.86</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>19.24</v>
+        <v>0.87</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>19.64</v>
+        <v>0.87</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>19.98</v>
+        <v>0.89</v>
       </c>
       <c r="Z9" s="5" t="n">
-        <v>20.11</v>
+        <v>0.91</v>
       </c>
       <c r="AA9" s="5" t="inlineStr">
         <is>
@@ -3064,167 +3059,726 @@
         </is>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>16.9844</v>
+        <v>1.8684</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>8.390000000000001</v>
+        <v>-53.44</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>56600577</v>
+        <v>103526167</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>55223005</v>
+        <v>130019425</v>
       </c>
       <c r="AL9" s="5" t="inlineStr">
         <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="AM9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM9" s="5" t="inlineStr"/>
       <c r="AN9" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 27-08-26 tarihinde yükselen destek (17-04-26–13-08-26, ~%2.5 yükseliş, 3 temas) çizgisini aşağı kırdı. OBV düşüşte; doğruluyor.</t>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO9" s="5" t="inlineStr"/>
       <c r="AP9" s="7" t="inlineStr">
         <is>
-          <t>▼ 11-08-26</t>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AQ9" s="5" t="inlineStr"/>
       <c r="AR9" s="7" t="inlineStr">
         <is>
-          <t>▼ 12-08-26</t>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AS9" s="5" t="inlineStr"/>
       <c r="AT9" s="7" t="inlineStr">
         <is>
-          <t>▼ 13-08-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AU9" s="5" t="inlineStr"/>
       <c r="AV9" s="7" t="inlineStr">
         <is>
-          <t>▼ 17-08-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AW9" s="5" t="inlineStr"/>
-      <c r="AX9" s="7" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
-        </is>
-      </c>
-      <c r="AY9" s="5" t="inlineStr"/>
-      <c r="AZ9" s="5" t="inlineStr"/>
-      <c r="BA9" s="5" t="inlineStr"/>
+      <c r="AX9" s="5" t="inlineStr"/>
+      <c r="AY9" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ9" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA9" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BB9" s="5" t="inlineStr"/>
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
-      <c r="BE9" s="5" t="inlineStr"/>
+      <c r="BE9" s="5" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
       <c r="BF9" s="5" t="inlineStr"/>
       <c r="BG9" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BH9" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BI9" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BJ9" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BK9" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BL9" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM9" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BN9" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BO9" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BP9" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BQ9" s="5" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BR9" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BS9" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BT9" s="5" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BU9" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BV9" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BW9" s="5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BX9" s="5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BY9" s="5" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BZ9" s="5" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CA9" s="5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CB9" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC9" s="5" t="inlineStr">
+        <is>
+          <t>T23 23-07-26 @0.95</t>
+        </is>
+      </c>
+      <c r="CD9" s="5" t="inlineStr">
+        <is>
+          <t>D24 11-08-26 @0.83</t>
+        </is>
+      </c>
+      <c r="CE9" s="5" t="inlineStr">
+        <is>
+          <t>17-08-26</t>
+        </is>
+      </c>
+      <c r="CF9" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CG9" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="CH9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>ACSEL</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>-2.4664</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>4.4624</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>-41.13</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-43.48</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>-164.92</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-169.42</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>120.67</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>121.33</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>125.19</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>127.73</v>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>126.2057</v>
+      </c>
+      <c r="AH10" s="3" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>124528</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>185574</v>
+      </c>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 24-08-26 tarihinde düşen trend (02-06-26–14-08-26, ~%31.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseldi; birikim işareti.</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 10-08-26</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 10-06-26</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 23-06-26</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 07-07-26</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 27-07-26</t>
+        </is>
+      </c>
+      <c r="AY10" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ10" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr"/>
+      <c r="BC10" s="3" t="inlineStr"/>
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr"/>
+      <c r="BF10" s="3" t="inlineStr">
+        <is>
+          <t>5-8</t>
+        </is>
+      </c>
+      <c r="BG10" s="3" t="n">
+        <v>120.63</v>
+      </c>
+      <c r="BH10" s="3" t="n">
+        <v>121.37</v>
+      </c>
+      <c r="BI10" s="3" t="n">
+        <v>122.53</v>
+      </c>
+      <c r="BJ10" s="3" t="n">
+        <v>123.27</v>
+      </c>
+      <c r="BK10" s="3" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="BL10" s="3" t="n">
+        <v>118.73</v>
+      </c>
+      <c r="BM10" s="3" t="n">
+        <v>117.57</v>
+      </c>
+      <c r="BN10" s="3" t="n">
+        <v>121.33</v>
+      </c>
+      <c r="BO10" s="3" t="n">
+        <v>122.87</v>
+      </c>
+      <c r="BP10" s="3" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="BQ10" s="3" t="n">
+        <v>127.07</v>
+      </c>
+      <c r="BR10" s="3" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="BS10" s="3" t="n">
+        <v>117.13</v>
+      </c>
+      <c r="BT10" s="3" t="n">
+        <v>114.47</v>
+      </c>
+      <c r="BU10" s="3" t="n">
+        <v>120.53</v>
+      </c>
+      <c r="BV10" s="3" t="n">
+        <v>129.57</v>
+      </c>
+      <c r="BW10" s="3" t="n">
+        <v>138.93</v>
+      </c>
+      <c r="BX10" s="3" t="n">
+        <v>147.97</v>
+      </c>
+      <c r="BY10" s="3" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="BZ10" s="3" t="n">
+        <v>102.13</v>
+      </c>
+      <c r="CA10" s="3" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="CB10" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC10" s="3" t="inlineStr">
+        <is>
+          <t>T37 25-08-26 @124.0</t>
+        </is>
+      </c>
+      <c r="CD10" s="3" t="inlineStr">
+        <is>
+          <t>D30 19-08-26 @111.5</t>
+        </is>
+      </c>
+      <c r="CE10" s="3" t="inlineStr">
+        <is>
+          <t>24-08-26</t>
+        </is>
+      </c>
+      <c r="CF10" s="3" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="CG10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="CH10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Aşağı kırılım</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.6385999999999999</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-0.1405</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>-44.67</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>-41.73</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>-133.9</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>-131.16</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="Z11" s="5" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="5" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG11" s="5" t="n">
+        <v>16.9844</v>
+      </c>
+      <c r="AH11" s="5" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AI11" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ11" s="5" t="n">
+        <v>56600577</v>
+      </c>
+      <c r="AK11" s="5" t="n">
+        <v>55223005</v>
+      </c>
+      <c r="AL11" s="5" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN11" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 27-08-26 tarihinde yükselen destek (17-04-26–13-08-26, ~%2.5 yükseliş, 3 temas) çizgisini aşağı kırdı. OBV düşüşte; doğruluyor.</t>
+        </is>
+      </c>
+      <c r="AO11" s="5" t="inlineStr"/>
+      <c r="AP11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 11-08-26</t>
+        </is>
+      </c>
+      <c r="AQ11" s="5" t="inlineStr"/>
+      <c r="AR11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 12-08-26</t>
+        </is>
+      </c>
+      <c r="AS11" s="5" t="inlineStr"/>
+      <c r="AT11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 13-08-26</t>
+        </is>
+      </c>
+      <c r="AU11" s="5" t="inlineStr"/>
+      <c r="AV11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 17-08-26</t>
+        </is>
+      </c>
+      <c r="AW11" s="5" t="inlineStr"/>
+      <c r="AX11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
+      <c r="AY11" s="5" t="inlineStr"/>
+      <c r="AZ11" s="5" t="inlineStr"/>
+      <c r="BA11" s="5" t="inlineStr"/>
+      <c r="BB11" s="5" t="inlineStr"/>
+      <c r="BC11" s="5" t="inlineStr"/>
+      <c r="BD11" s="5" t="inlineStr"/>
+      <c r="BE11" s="5" t="inlineStr"/>
+      <c r="BF11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="n">
         <v>18.47</v>
       </c>
-      <c r="BH9" s="5" t="n">
+      <c r="BH11" s="5" t="n">
         <v>18.61</v>
       </c>
-      <c r="BI9" s="5" t="n">
+      <c r="BI11" s="5" t="n">
         <v>18.82</v>
       </c>
-      <c r="BJ9" s="5" t="n">
+      <c r="BJ11" s="5" t="n">
         <v>18.96</v>
       </c>
-      <c r="BK9" s="5" t="n">
+      <c r="BK11" s="5" t="n">
         <v>18.26</v>
       </c>
-      <c r="BL9" s="5" t="n">
+      <c r="BL11" s="5" t="n">
         <v>18.12</v>
       </c>
-      <c r="BM9" s="5" t="n">
+      <c r="BM11" s="5" t="n">
         <v>17.91</v>
       </c>
-      <c r="BN9" s="5" t="n">
+      <c r="BN11" s="5" t="n">
         <v>18.66</v>
       </c>
-      <c r="BO9" s="5" t="n">
+      <c r="BO11" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="BP9" s="5" t="n">
+      <c r="BP11" s="5" t="n">
         <v>19.59</v>
       </c>
-      <c r="BQ9" s="5" t="n">
+      <c r="BQ11" s="5" t="n">
         <v>19.93</v>
       </c>
-      <c r="BR9" s="5" t="n">
+      <c r="BR11" s="5" t="n">
         <v>18.07</v>
       </c>
-      <c r="BS9" s="5" t="n">
+      <c r="BS11" s="5" t="n">
         <v>17.73</v>
       </c>
-      <c r="BT9" s="5" t="n">
+      <c r="BT11" s="5" t="n">
         <v>17.14</v>
       </c>
-      <c r="BU9" s="5" t="n">
+      <c r="BU11" s="5" t="n">
         <v>19.75</v>
       </c>
-      <c r="BV9" s="5" t="n">
+      <c r="BV11" s="5" t="n">
         <v>21.18</v>
       </c>
-      <c r="BW9" s="5" t="n">
+      <c r="BW11" s="5" t="n">
         <v>23.95</v>
       </c>
-      <c r="BX9" s="5" t="n">
+      <c r="BX11" s="5" t="n">
         <v>25.38</v>
       </c>
-      <c r="BY9" s="5" t="n">
+      <c r="BY11" s="5" t="n">
         <v>16.98</v>
       </c>
-      <c r="BZ9" s="5" t="n">
+      <c r="BZ11" s="5" t="n">
         <v>15.55</v>
       </c>
-      <c r="CA9" s="5" t="n">
+      <c r="CA11" s="5" t="n">
         <v>12.78</v>
       </c>
-      <c r="CB9" s="7" t="inlineStr">
+      <c r="CB11" s="7" t="inlineStr">
         <is>
           <t>▼</t>
         </is>
       </c>
-      <c r="CC9" s="5" t="inlineStr">
+      <c r="CC11" s="5" t="inlineStr">
         <is>
           <t>T28 19-08-26 @19.61</t>
         </is>
       </c>
-      <c r="CD9" s="5" t="inlineStr">
+      <c r="CD11" s="5" t="inlineStr">
         <is>
           <t>D31 13-08-26 @18.74</t>
         </is>
       </c>
-      <c r="CE9" s="5" t="inlineStr">
+      <c r="CE11" s="5" t="inlineStr">
         <is>
           <t>27-08-26</t>
         </is>
       </c>
-      <c r="CF9" s="5" t="n">
+      <c r="CF11" s="5" t="n">
         <v>18.53</v>
       </c>
-      <c r="CG9" s="5" t="n">
+      <c r="CG11" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="CH9" s="5" t="inlineStr"/>
-      <c r="CI9" s="5" t="inlineStr"/>
+      <c r="CH11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CI9"/>
+  <autoFilter ref="A1:CH11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3235,7 +3789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI1"/>
+  <dimension ref="A1:CH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3324,7 +3878,6 @@
     <col width="16" customWidth="1" min="84" max="84"/>
     <col width="20" customWidth="1" min="85" max="85"/>
     <col width="13" customWidth="1" min="86" max="86"/>
-    <col width="6" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3758,14 +4311,9 @@
           <t>OBV kırılım</t>
         </is>
       </c>
-      <c r="CI1" s="2" t="inlineStr">
-        <is>
-          <t>Hata</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CI1"/>
+  <autoFilter ref="A1:CH1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3776,7 +4324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI11"/>
+  <dimension ref="A1:CH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3804,7 +4352,7 @@
     <col width="8" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
     <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="7" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
     <col width="5" customWidth="1" min="27" max="27"/>
     <col width="6" customWidth="1" min="28" max="28"/>
     <col width="7" customWidth="1" min="29" max="29"/>
@@ -3865,7 +4413,6 @@
     <col width="16" customWidth="1" min="84" max="84"/>
     <col width="20" customWidth="1" min="85" max="85"/>
     <col width="13" customWidth="1" min="86" max="86"/>
-    <col width="18" customWidth="1" min="87" max="87"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4297,11 +4844,6 @@
       <c r="CH1" s="2" t="inlineStr">
         <is>
           <t>OBV kırılım</t>
-        </is>
-      </c>
-      <c r="CI1" s="2" t="inlineStr">
-        <is>
-          <t>Hata</t>
         </is>
       </c>
     </row>
@@ -4576,7 +5118,6 @@
           <t>21-08-26</t>
         </is>
       </c>
-      <c r="CI2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -4853,19 +5394,18 @@
           <t>14-08-26</t>
         </is>
       </c>
-      <c r="CI3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>A1CAP</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>35.44</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1.72</v>
+        <v>2.86</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -4876,67 +5416,67 @@
         <v>94</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>23.15</v>
+        <v>7.98</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>61.33</v>
+        <v>47.78</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1.2997</v>
+        <v>-0.2832</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3751</v>
+        <v>0.099</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>6.94</v>
+        <v>7.73</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1.7785</v>
+        <v>0.2781</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>5.02</v>
+        <v>3.22</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>37.93</v>
+        <v>22.59</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>39.34</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>65.17</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>52.35</v>
+        <v>-24.38</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>53.21</v>
+        <v>-36.54</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-0.86</v>
+        <v>12.15</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>151.57</v>
+        <v>-287.49</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>149.19</v>
+        <v>-363.06</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>35.39</v>
+        <v>8.44</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>34.96</v>
+        <v>8.4</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>34.22</v>
+        <v>8.42</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>33.37</v>
+        <v>8.57</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>32.81</v>
+        <v>8.9</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>32.91</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -4945,17 +5485,17 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr">
@@ -4965,27 +5505,27 @@
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>37.0379</v>
+        <v>11.1687</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-4.31</v>
+        <v>-22.64</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>2.86</v>
+        <v>0.87</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>10999396</v>
+        <v>6736736</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>3843601</v>
+        <v>7700768</v>
       </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -4995,158 +5535,161 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
+          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="4" t="inlineStr">
         <is>
-          <t>▲ 07-08-26</t>
+          <t>▲ 26-08-26</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 07-08-26</t>
+      <c r="AR4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 12-08-26</t>
+      <c r="AT4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 09-07-26</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20-08-26</t>
+      <c r="AV4" s="8" t="inlineStr">
+        <is>
+          <t>▼ 27-03-26</t>
         </is>
       </c>
       <c r="AW4" s="3" t="inlineStr"/>
       <c r="AX4" s="8" t="inlineStr">
         <is>
-          <t>▼ 02-06-26</t>
-        </is>
-      </c>
-      <c r="AY4" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+          <t>▼ 24-04-26</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr"/>
       <c r="AZ4" s="3" t="inlineStr"/>
       <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr"/>
+      <c r="BB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BC4" s="3" t="inlineStr"/>
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="BF4" s="3" t="inlineStr"/>
       <c r="BG4" s="3" t="n">
-        <v>35.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BH4" s="3" t="n">
-        <v>36.27</v>
+        <v>8.73</v>
       </c>
       <c r="BI4" s="3" t="n">
-        <v>37.11</v>
+        <v>8.81</v>
       </c>
       <c r="BJ4" s="3" t="n">
-        <v>37.81</v>
+        <v>8.99</v>
       </c>
       <c r="BK4" s="3" t="n">
-        <v>34.73</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="BL4" s="3" t="n">
-        <v>34.03</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BM4" s="3" t="n">
-        <v>33.19</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BN4" s="3" t="n">
-        <v>36.03</v>
+        <v>8.49</v>
       </c>
       <c r="BO4" s="3" t="n">
-        <v>38.51</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="BP4" s="3" t="n">
-        <v>41.57</v>
+        <v>8.94</v>
       </c>
       <c r="BQ4" s="3" t="n">
-        <v>44.05</v>
+        <v>9.24</v>
       </c>
       <c r="BR4" s="3" t="n">
-        <v>32.97</v>
+        <v>8.34</v>
       </c>
       <c r="BS4" s="3" t="n">
-        <v>30.49</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="BT4" s="3" t="n">
-        <v>27.43</v>
+        <v>7.89</v>
       </c>
       <c r="BU4" s="3" t="n">
-        <v>34.31</v>
+        <v>8.66</v>
       </c>
       <c r="BV4" s="3" t="n">
-        <v>40.23</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BW4" s="3" t="n">
-        <v>45.01</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="BX4" s="3" t="n">
-        <v>50.93</v>
+        <v>10.6</v>
       </c>
       <c r="BY4" s="3" t="n">
-        <v>29.53</v>
+        <v>8</v>
       </c>
       <c r="BZ4" s="3" t="n">
-        <v>23.61</v>
+        <v>7.36</v>
       </c>
       <c r="CA4" s="3" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="CB4" s="8" t="inlineStr">
-        <is>
-          <t>▼</t>
+        <v>6.7</v>
+      </c>
+      <c r="CB4" s="4" t="inlineStr">
+        <is>
+          <t>▲</t>
         </is>
       </c>
       <c r="CC4" s="3" t="inlineStr">
         <is>
-          <t>T31 25-08-26 @39.1</t>
+          <t>T26 18-08-26 @8.45</t>
         </is>
       </c>
       <c r="CD4" s="3" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @28.4</t>
+          <t>D28 31-07-26 @8.58</t>
         </is>
       </c>
       <c r="CE4" s="3" t="inlineStr">
         <is>
-          <t>07-08-26</t>
+          <t>26-08-26</t>
         </is>
       </c>
       <c r="CF4" s="3" t="n">
-        <v>32.42</v>
+        <v>8.43</v>
       </c>
       <c r="CG4" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="CH4" s="3" t="inlineStr"/>
-      <c r="CI4" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="CH4" s="3" t="inlineStr">
+        <is>
+          <t>26-08-26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>ADEL</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>35.44</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2.86</v>
+        <v>1.72</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -5157,67 +5700,67 @@
         <v>94</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>7.98</v>
+        <v>23.15</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>47.78</v>
+        <v>61.33</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-0.2832</v>
+        <v>1.2997</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.099</v>
+        <v>0.3751</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>7.73</v>
+        <v>6.94</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.2781</v>
+        <v>1.7785</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3.22</v>
+        <v>5.02</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>22.59</v>
+        <v>37.93</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>98.43000000000001</v>
+        <v>39.34</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>86.15000000000001</v>
+        <v>65.17</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-24.38</v>
+        <v>52.35</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>-36.54</v>
+        <v>53.21</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>12.15</v>
+        <v>-0.86</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>-287.49</v>
+        <v>151.57</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>-363.06</v>
+        <v>149.19</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>8.44</v>
+        <v>35.39</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>8.4</v>
+        <v>34.96</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>8.42</v>
+        <v>34.22</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>8.57</v>
+        <v>33.37</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>8.9</v>
+        <v>32.81</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>9.460000000000001</v>
+        <v>32.91</v>
       </c>
       <c r="AA5" s="5" t="inlineStr">
         <is>
@@ -5226,47 +5769,47 @@
       </c>
       <c r="AB5" s="5" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AE5" s="5" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE5" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF5" s="5" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>11.1687</v>
+        <v>37.0379</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>-22.64</v>
+        <v>-4.31</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>0.87</v>
+        <v>2.86</v>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>6736736</v>
+        <v>10999396</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>7700768</v>
+        <v>3843601</v>
       </c>
       <c r="AL5" s="5" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="AM5" s="5" t="inlineStr">
@@ -5276,162 +5819,157 @@
       </c>
       <c r="AN5" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 26-08-26 tarihinde düşen trend (24-02-26–07-08-26, ~%50.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 26-08-26 tarihinde önceden kırmıştı. Not: 1 çizgi fitil ihlali nedeniyle sonlandırıldı.</t>
+          <t>Fiyat 07-08-26 tarihinde düşen trend (09-06-26–18-06-26, ~%2.1 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. Hacim ortalamanın üzerinde.</t>
         </is>
       </c>
       <c r="AO5" s="5" t="inlineStr"/>
       <c r="AP5" s="6" t="inlineStr">
         <is>
-          <t>▲ 26-08-26</t>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AQ5" s="5" t="inlineStr"/>
-      <c r="AR5" s="7" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AR5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 07-08-26</t>
         </is>
       </c>
       <c r="AS5" s="5" t="inlineStr"/>
-      <c r="AT5" s="7" t="inlineStr">
-        <is>
-          <t>▼ 09-07-26</t>
+      <c r="AT5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 12-08-26</t>
         </is>
       </c>
       <c r="AU5" s="5" t="inlineStr"/>
-      <c r="AV5" s="7" t="inlineStr">
-        <is>
-          <t>▼ 27-03-26</t>
+      <c r="AV5" s="6" t="inlineStr">
+        <is>
+          <t>▲ 20-08-26</t>
         </is>
       </c>
       <c r="AW5" s="5" t="inlineStr"/>
       <c r="AX5" s="7" t="inlineStr">
         <is>
-          <t>▼ 24-04-26</t>
-        </is>
-      </c>
-      <c r="AY5" s="5" t="inlineStr"/>
+          <t>▼ 02-06-26</t>
+        </is>
+      </c>
+      <c r="AY5" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="AZ5" s="5" t="inlineStr"/>
       <c r="BA5" s="5" t="inlineStr"/>
-      <c r="BB5" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="BB5" s="5" t="inlineStr"/>
       <c r="BC5" s="5" t="inlineStr"/>
       <c r="BD5" s="5" t="inlineStr"/>
       <c r="BE5" s="5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BF5" s="5" t="inlineStr"/>
       <c r="BG5" s="5" t="n">
-        <v>8.550000000000001</v>
+        <v>35.57</v>
       </c>
       <c r="BH5" s="5" t="n">
-        <v>8.73</v>
+        <v>36.27</v>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>8.81</v>
+        <v>37.11</v>
       </c>
       <c r="BJ5" s="5" t="n">
-        <v>8.99</v>
+        <v>37.81</v>
       </c>
       <c r="BK5" s="5" t="n">
-        <v>8.470000000000001</v>
+        <v>34.73</v>
       </c>
       <c r="BL5" s="5" t="n">
-        <v>8.289999999999999</v>
+        <v>34.03</v>
       </c>
       <c r="BM5" s="5" t="n">
-        <v>8.210000000000001</v>
+        <v>33.19</v>
       </c>
       <c r="BN5" s="5" t="n">
-        <v>8.49</v>
+        <v>36.03</v>
       </c>
       <c r="BO5" s="5" t="n">
-        <v>8.789999999999999</v>
+        <v>38.51</v>
       </c>
       <c r="BP5" s="5" t="n">
-        <v>8.94</v>
+        <v>41.57</v>
       </c>
       <c r="BQ5" s="5" t="n">
-        <v>9.24</v>
+        <v>44.05</v>
       </c>
       <c r="BR5" s="5" t="n">
-        <v>8.34</v>
+        <v>32.97</v>
       </c>
       <c r="BS5" s="5" t="n">
-        <v>8.039999999999999</v>
+        <v>30.49</v>
       </c>
       <c r="BT5" s="5" t="n">
-        <v>7.89</v>
+        <v>27.43</v>
       </c>
       <c r="BU5" s="5" t="n">
-        <v>8.66</v>
+        <v>34.31</v>
       </c>
       <c r="BV5" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>40.23</v>
       </c>
       <c r="BW5" s="5" t="n">
-        <v>9.960000000000001</v>
+        <v>45.01</v>
       </c>
       <c r="BX5" s="5" t="n">
-        <v>10.6</v>
+        <v>50.93</v>
       </c>
       <c r="BY5" s="5" t="n">
-        <v>8</v>
+        <v>29.53</v>
       </c>
       <c r="BZ5" s="5" t="n">
-        <v>7.36</v>
+        <v>23.61</v>
       </c>
       <c r="CA5" s="5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="CB5" s="6" t="inlineStr">
-        <is>
-          <t>▲</t>
+        <v>18.83</v>
+      </c>
+      <c r="CB5" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
         </is>
       </c>
       <c r="CC5" s="5" t="inlineStr">
         <is>
-          <t>T26 18-08-26 @8.45</t>
+          <t>T31 25-08-26 @39.1</t>
         </is>
       </c>
       <c r="CD5" s="5" t="inlineStr">
         <is>
-          <t>D28 31-07-26 @8.58</t>
+          <t>D28 31-07-26 @28.4</t>
         </is>
       </c>
       <c r="CE5" s="5" t="inlineStr">
         <is>
-          <t>26-08-26</t>
+          <t>07-08-26</t>
         </is>
       </c>
       <c r="CF5" s="5" t="n">
-        <v>8.43</v>
+        <v>32.42</v>
       </c>
       <c r="CG5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CH5" s="5" t="inlineStr">
-        <is>
-          <t>26-08-26</t>
-        </is>
-      </c>
-      <c r="CI5" s="5" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="CH5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>AFYON</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.69</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1.16</v>
+        <v>-0.08</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -5439,239 +5977,243 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6.1</v>
+        <v>1.71</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>47.84</v>
+        <v>50.78</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.0107</v>
+        <v>-0.0058</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0032</v>
+        <v>0.0382</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.031</v>
+        <v>0.3216</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3.56</v>
+        <v>2.53</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>30.22</v>
+        <v>16.8</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>51.52</v>
+        <v>58.09</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>46.08</v>
+        <v>61.75</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>-20.93</v>
+        <v>1.03</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>-21.65</v>
+        <v>-2.32</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.72</v>
+        <v>3.35</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>-3.73</v>
+        <v>12.78</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>-14.64</v>
+        <v>-13.07</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>0.86</v>
+        <v>12.7</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>0.86</v>
+        <v>12.67</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.65</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.64</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0.89</v>
+        <v>12.69</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.83</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
+      <c r="AE6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>14.073</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>-9.83</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>1998004</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>1569436</v>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
           <t>0/5</t>
         </is>
       </c>
-      <c r="AG6" s="3" t="n">
-        <v>1.8684</v>
-      </c>
-      <c r="AH6" s="3" t="n">
-        <v>-53.44</v>
-      </c>
-      <c r="AI6" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>103526167</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>130019425</v>
-      </c>
-      <c r="AL6" s="3" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
+          <t>Fiyat 21-08-26 tarihinde düşen trend (21-04-26–14-08-26, ~%12.2 düşüş, 4 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor. OBV 21-08-26 tarihinde önceden kırmıştı.</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AP6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
+      <c r="AR6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21-08-26</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="8" t="inlineStr">
-        <is>
-          <t>▼ 21-05-26</t>
+      <c r="AT6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 27-08-26</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr"/>
       <c r="AV6" s="8" t="inlineStr">
         <is>
-          <t>▼ 21-05-26</t>
+          <t>▼ 09-04-26</t>
         </is>
       </c>
       <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="AZ6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
-      <c r="BA6" s="4" t="inlineStr">
-        <is>
-          <t>▲</t>
-        </is>
-      </c>
+      <c r="AX6" s="8" t="inlineStr">
+        <is>
+          <t>▼ 22-04-26</t>
+        </is>
+      </c>
+      <c r="AY6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
       <c r="BB6" s="3" t="inlineStr"/>
-      <c r="BC6" s="3" t="inlineStr"/>
+      <c r="BC6" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
       <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>5-8-13</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr"/>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>5-34</t>
+        </is>
+      </c>
       <c r="BG6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.73</v>
       </c>
       <c r="BH6" s="3" t="n">
-        <v>0.89</v>
+        <v>12.78</v>
       </c>
       <c r="BI6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.86</v>
       </c>
       <c r="BJ6" s="3" t="n">
-        <v>0.93</v>
+        <v>12.91</v>
       </c>
       <c r="BK6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.65</v>
       </c>
       <c r="BL6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.6</v>
       </c>
       <c r="BM6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>12.52</v>
       </c>
       <c r="BN6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.91</v>
       </c>
       <c r="BO6" s="3" t="n">
-        <v>0.89</v>
+        <v>13.17</v>
       </c>
       <c r="BP6" s="3" t="n">
-        <v>0.91</v>
+        <v>13.65</v>
       </c>
       <c r="BQ6" s="3" t="n">
-        <v>0.93</v>
+        <v>13.91</v>
       </c>
       <c r="BR6" s="3" t="n">
-        <v>0.85</v>
+        <v>12.43</v>
       </c>
       <c r="BS6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.17</v>
       </c>
       <c r="BT6" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>11.69</v>
       </c>
       <c r="BU6" s="3" t="n">
-        <v>0.87</v>
+        <v>12.73</v>
       </c>
       <c r="BV6" s="3" t="n">
-        <v>0.92</v>
+        <v>13.35</v>
       </c>
       <c r="BW6" s="3" t="n">
-        <v>0.96</v>
+        <v>14</v>
       </c>
       <c r="BX6" s="3" t="n">
-        <v>1.01</v>
+        <v>14.62</v>
       </c>
       <c r="BY6" s="3" t="n">
-        <v>0.83</v>
+        <v>12.08</v>
       </c>
       <c r="BZ6" s="3" t="n">
-        <v>0.78</v>
+        <v>11.46</v>
       </c>
       <c r="CA6" s="3" t="n">
-        <v>0.74</v>
+        <v>10.81</v>
       </c>
       <c r="CB6" s="8" t="inlineStr">
         <is>
@@ -5680,27 +6222,30 @@
       </c>
       <c r="CC6" s="3" t="inlineStr">
         <is>
-          <t>T23 23-07-26 @0.95</t>
+          <t>T24 24-08-26 @13.39</t>
         </is>
       </c>
       <c r="CD6" s="3" t="inlineStr">
         <is>
-          <t>D24 11-08-26 @0.83</t>
+          <t>D29 18-08-26 @12.28</t>
         </is>
       </c>
       <c r="CE6" s="3" t="inlineStr">
         <is>
-          <t>17-08-26</t>
+          <t>21-08-26</t>
         </is>
       </c>
       <c r="CF6" s="3" t="n">
-        <v>0.91</v>
+        <v>12.98</v>
       </c>
       <c r="CG6" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="CH6" s="3" t="inlineStr"/>
-      <c r="CI6" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="CH6" s="3" t="inlineStr">
+        <is>
+          <t>21-08-26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -5977,7 +6522,6 @@
         <v>7</v>
       </c>
       <c r="CH7" s="5" t="inlineStr"/>
-      <c r="CI7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -6254,90 +6798,89 @@
           <t>05-08-26</t>
         </is>
       </c>
-      <c r="CI8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>AEFES</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>18.41</v>
+        <v>0.87</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.65</v>
+        <v>1.16</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Aşağı kırılım</t>
+          <t>Kırılım</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-2.1</v>
+        <v>6.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>31.61</v>
+        <v>47.84</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>-0.6385999999999999</v>
+        <v>-0.0107</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>-0.1405</v>
+        <v>0.0032</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-4.76</v>
+        <v>1.16</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.6009</v>
+        <v>0.031</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3.26</v>
+        <v>3.56</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>25.27</v>
+        <v>30.22</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>3.89</v>
+        <v>51.52</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>6.99</v>
+        <v>46.08</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>-44.67</v>
+        <v>-20.93</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>-41.73</v>
+        <v>-21.65</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>-2.94</v>
+        <v>0.72</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>-133.9</v>
+        <v>-3.73</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>-131.16</v>
+        <v>-14.64</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>18.71</v>
+        <v>0.86</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>18.9</v>
+        <v>0.86</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>19.24</v>
+        <v>0.87</v>
       </c>
       <c r="X9" s="5" t="n">
-        <v>19.64</v>
+        <v>0.87</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>19.98</v>
+        <v>0.89</v>
       </c>
       <c r="Z9" s="5" t="n">
-        <v>20.11</v>
+        <v>0.91</v>
       </c>
       <c r="AA9" s="5" t="inlineStr">
         <is>
@@ -6370,135 +6913,143 @@
         </is>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>16.9844</v>
+        <v>1.8684</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>8.390000000000001</v>
+        <v>-53.44</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>1.02</v>
+        <v>0.8</v>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>56600577</v>
+        <v>103526167</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>55223005</v>
+        <v>130019425</v>
       </c>
       <c r="AL9" s="5" t="inlineStr">
         <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="AM9" s="5" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>2/5</t>
+        </is>
+      </c>
+      <c r="AM9" s="5" t="inlineStr"/>
       <c r="AN9" s="5" t="inlineStr">
         <is>
-          <t>Fiyat 27-08-26 tarihinde yükselen destek (17-04-26–13-08-26, ~%2.5 yükseliş, 3 temas) çizgisini aşağı kırdı. OBV düşüşte; doğruluyor.</t>
+          <t>Fiyat 17-08-26 tarihinde düşen trend (11-05-26–23-07-26, ~%20.2 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseliyor; doğruluyor.</t>
         </is>
       </c>
       <c r="AO9" s="5" t="inlineStr"/>
       <c r="AP9" s="7" t="inlineStr">
         <is>
-          <t>▼ 11-08-26</t>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AQ9" s="5" t="inlineStr"/>
       <c r="AR9" s="7" t="inlineStr">
         <is>
-          <t>▼ 12-08-26</t>
+          <t>▼ 24-08-26</t>
         </is>
       </c>
       <c r="AS9" s="5" t="inlineStr"/>
       <c r="AT9" s="7" t="inlineStr">
         <is>
-          <t>▼ 13-08-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AU9" s="5" t="inlineStr"/>
       <c r="AV9" s="7" t="inlineStr">
         <is>
-          <t>▼ 17-08-26</t>
+          <t>▼ 21-05-26</t>
         </is>
       </c>
       <c r="AW9" s="5" t="inlineStr"/>
-      <c r="AX9" s="7" t="inlineStr">
-        <is>
-          <t>▼ 24-08-26</t>
-        </is>
-      </c>
-      <c r="AY9" s="5" t="inlineStr"/>
-      <c r="AZ9" s="5" t="inlineStr"/>
-      <c r="BA9" s="5" t="inlineStr"/>
+      <c r="AX9" s="5" t="inlineStr"/>
+      <c r="AY9" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="AZ9" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
+      <c r="BA9" s="6" t="inlineStr">
+        <is>
+          <t>▲</t>
+        </is>
+      </c>
       <c r="BB9" s="5" t="inlineStr"/>
       <c r="BC9" s="5" t="inlineStr"/>
       <c r="BD9" s="5" t="inlineStr"/>
-      <c r="BE9" s="5" t="inlineStr"/>
+      <c r="BE9" s="5" t="inlineStr">
+        <is>
+          <t>5-8-13</t>
+        </is>
+      </c>
       <c r="BF9" s="5" t="inlineStr"/>
       <c r="BG9" s="5" t="n">
-        <v>18.47</v>
+        <v>0.87</v>
       </c>
       <c r="BH9" s="5" t="n">
-        <v>18.61</v>
+        <v>0.89</v>
       </c>
       <c r="BI9" s="5" t="n">
-        <v>18.82</v>
+        <v>0.91</v>
       </c>
       <c r="BJ9" s="5" t="n">
-        <v>18.96</v>
+        <v>0.93</v>
       </c>
       <c r="BK9" s="5" t="n">
-        <v>18.26</v>
+        <v>0.85</v>
       </c>
       <c r="BL9" s="5" t="n">
-        <v>18.12</v>
+        <v>0.83</v>
       </c>
       <c r="BM9" s="5" t="n">
-        <v>17.91</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN9" s="5" t="n">
-        <v>18.66</v>
+        <v>0.87</v>
       </c>
       <c r="BO9" s="5" t="n">
-        <v>19</v>
+        <v>0.89</v>
       </c>
       <c r="BP9" s="5" t="n">
-        <v>19.59</v>
+        <v>0.91</v>
       </c>
       <c r="BQ9" s="5" t="n">
-        <v>19.93</v>
+        <v>0.93</v>
       </c>
       <c r="BR9" s="5" t="n">
-        <v>18.07</v>
+        <v>0.85</v>
       </c>
       <c r="BS9" s="5" t="n">
-        <v>17.73</v>
+        <v>0.83</v>
       </c>
       <c r="BT9" s="5" t="n">
-        <v>17.14</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BU9" s="5" t="n">
-        <v>19.75</v>
+        <v>0.87</v>
       </c>
       <c r="BV9" s="5" t="n">
-        <v>21.18</v>
+        <v>0.92</v>
       </c>
       <c r="BW9" s="5" t="n">
-        <v>23.95</v>
+        <v>0.96</v>
       </c>
       <c r="BX9" s="5" t="n">
-        <v>25.38</v>
+        <v>1.01</v>
       </c>
       <c r="BY9" s="5" t="n">
-        <v>16.98</v>
+        <v>0.83</v>
       </c>
       <c r="BZ9" s="5" t="n">
-        <v>15.55</v>
+        <v>0.78</v>
       </c>
       <c r="CA9" s="5" t="n">
-        <v>12.78</v>
+        <v>0.74</v>
       </c>
       <c r="CB9" s="7" t="inlineStr">
         <is>
@@ -6507,27 +7058,26 @@
       </c>
       <c r="CC9" s="5" t="inlineStr">
         <is>
-          <t>T28 19-08-26 @19.61</t>
+          <t>T23 23-07-26 @0.95</t>
         </is>
       </c>
       <c r="CD9" s="5" t="inlineStr">
         <is>
-          <t>D31 13-08-26 @18.74</t>
+          <t>D24 11-08-26 @0.83</t>
         </is>
       </c>
       <c r="CE9" s="5" t="inlineStr">
         <is>
-          <t>27-08-26</t>
+          <t>17-08-26</t>
         </is>
       </c>
       <c r="CF9" s="5" t="n">
-        <v>18.53</v>
+        <v>0.91</v>
       </c>
       <c r="CG9" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="CH9" s="5" t="inlineStr"/>
-      <c r="CI9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -6535,160 +7085,453 @@
           <t>ACSEL</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr"/>
-      <c r="C10" s="3" t="inlineStr"/>
+      <c r="B10" s="3" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-1.07</v>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr"/>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr"/>
-      <c r="Y10" s="3" t="inlineStr"/>
-      <c r="Z10" s="3" t="inlineStr"/>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr"/>
-      <c r="AD10" s="3" t="inlineStr"/>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
+          <t>Kırılım</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>-2.4664</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>4.4624</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>12.69</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>-41.13</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-43.48</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>-164.92</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-169.42</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>120.67</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>121.33</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>122.67</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>125.19</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>127.73</v>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>126.2057</v>
+      </c>
+      <c r="AH10" s="3" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>124528</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>185574</v>
+      </c>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>2/5</t>
+        </is>
+      </c>
       <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>Fiyat 24-08-26 tarihinde düşen trend (02-06-26–14-08-26, ~%31.9 düşüş, 3 temas) çizgisi yukarı kırıldı ve çizgi üzerinde tutunuyor. OBV yükseldi; birikim işareti.</t>
+        </is>
+      </c>
       <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AP10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 10-08-26</t>
+        </is>
+      </c>
       <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AR10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 10-06-26</t>
+        </is>
+      </c>
       <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AT10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 23-06-26</t>
+        </is>
+      </c>
       <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AV10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 07-07-26</t>
+        </is>
+      </c>
       <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="AX10" s="8" t="inlineStr">
+        <is>
+          <t>▼ 27-07-26</t>
+        </is>
+      </c>
+      <c r="AY10" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="AZ10" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
       <c r="BA10" s="3" t="inlineStr"/>
       <c r="BB10" s="3" t="inlineStr"/>
       <c r="BC10" s="3" t="inlineStr"/>
       <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr"/>
-      <c r="BF10" s="3" t="inlineStr"/>
-      <c r="BG10" s="3" t="inlineStr"/>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
-      <c r="BM10" s="3" t="inlineStr"/>
-      <c r="BN10" s="3" t="inlineStr"/>
-      <c r="BO10" s="3" t="inlineStr"/>
-      <c r="BP10" s="3" t="inlineStr"/>
-      <c r="BQ10" s="3" t="inlineStr"/>
-      <c r="BR10" s="3" t="inlineStr"/>
-      <c r="BS10" s="3" t="inlineStr"/>
-      <c r="BT10" s="3" t="inlineStr"/>
-      <c r="BU10" s="3" t="inlineStr"/>
-      <c r="BV10" s="3" t="inlineStr"/>
-      <c r="BW10" s="3" t="inlineStr"/>
-      <c r="BX10" s="3" t="inlineStr"/>
-      <c r="BY10" s="3" t="inlineStr"/>
-      <c r="BZ10" s="3" t="inlineStr"/>
-      <c r="CA10" s="3" t="inlineStr"/>
-      <c r="CB10" s="3" t="inlineStr"/>
-      <c r="CC10" s="3" t="inlineStr"/>
-      <c r="CD10" s="3" t="inlineStr"/>
-      <c r="CE10" s="3" t="inlineStr"/>
-      <c r="CF10" s="3" t="inlineStr"/>
-      <c r="CG10" s="3" t="inlineStr"/>
+      <c r="BF10" s="3" t="inlineStr">
+        <is>
+          <t>5-8</t>
+        </is>
+      </c>
+      <c r="BG10" s="3" t="n">
+        <v>120.63</v>
+      </c>
+      <c r="BH10" s="3" t="n">
+        <v>121.37</v>
+      </c>
+      <c r="BI10" s="3" t="n">
+        <v>122.53</v>
+      </c>
+      <c r="BJ10" s="3" t="n">
+        <v>123.27</v>
+      </c>
+      <c r="BK10" s="3" t="n">
+        <v>119.47</v>
+      </c>
+      <c r="BL10" s="3" t="n">
+        <v>118.73</v>
+      </c>
+      <c r="BM10" s="3" t="n">
+        <v>117.57</v>
+      </c>
+      <c r="BN10" s="3" t="n">
+        <v>121.33</v>
+      </c>
+      <c r="BO10" s="3" t="n">
+        <v>122.87</v>
+      </c>
+      <c r="BP10" s="3" t="n">
+        <v>125.53</v>
+      </c>
+      <c r="BQ10" s="3" t="n">
+        <v>127.07</v>
+      </c>
+      <c r="BR10" s="3" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="BS10" s="3" t="n">
+        <v>117.13</v>
+      </c>
+      <c r="BT10" s="3" t="n">
+        <v>114.47</v>
+      </c>
+      <c r="BU10" s="3" t="n">
+        <v>120.53</v>
+      </c>
+      <c r="BV10" s="3" t="n">
+        <v>129.57</v>
+      </c>
+      <c r="BW10" s="3" t="n">
+        <v>138.93</v>
+      </c>
+      <c r="BX10" s="3" t="n">
+        <v>147.97</v>
+      </c>
+      <c r="BY10" s="3" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="BZ10" s="3" t="n">
+        <v>102.13</v>
+      </c>
+      <c r="CA10" s="3" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="CB10" s="8" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC10" s="3" t="inlineStr">
+        <is>
+          <t>T37 25-08-26 @124.0</t>
+        </is>
+      </c>
+      <c r="CD10" s="3" t="inlineStr">
+        <is>
+          <t>D30 19-08-26 @111.5</t>
+        </is>
+      </c>
+      <c r="CE10" s="3" t="inlineStr">
+        <is>
+          <t>24-08-26</t>
+        </is>
+      </c>
+      <c r="CF10" s="3" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="CG10" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="CH10" s="3" t="inlineStr"/>
-      <c r="CI10" s="3" t="inlineStr">
-        <is>
-          <t>KeyError: 'kind'</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>AFYON</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="inlineStr"/>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.65</v>
+      </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>HATA</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="inlineStr"/>
-      <c r="O11" s="5" t="inlineStr"/>
-      <c r="P11" s="5" t="inlineStr"/>
-      <c r="Q11" s="5" t="inlineStr"/>
-      <c r="R11" s="5" t="inlineStr"/>
-      <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="5" t="inlineStr"/>
-      <c r="W11" s="5" t="inlineStr"/>
-      <c r="X11" s="5" t="inlineStr"/>
-      <c r="Y11" s="5" t="inlineStr"/>
-      <c r="Z11" s="5" t="inlineStr"/>
-      <c r="AA11" s="5" t="inlineStr"/>
-      <c r="AB11" s="5" t="inlineStr"/>
-      <c r="AC11" s="5" t="inlineStr"/>
-      <c r="AD11" s="5" t="inlineStr"/>
-      <c r="AE11" s="5" t="inlineStr"/>
-      <c r="AF11" s="5" t="inlineStr"/>
-      <c r="AG11" s="5" t="inlineStr"/>
-      <c r="AH11" s="5" t="inlineStr"/>
-      <c r="AI11" s="5" t="inlineStr"/>
-      <c r="AJ11" s="5" t="inlineStr"/>
-      <c r="AK11" s="5" t="inlineStr"/>
-      <c r="AL11" s="5" t="inlineStr"/>
-      <c r="AM11" s="5" t="inlineStr"/>
-      <c r="AN11" s="5" t="inlineStr"/>
+          <t>Aşağı kırılım</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>64</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>31.61</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.6385999999999999</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-0.1405</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>-44.67</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>-41.73</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>-133.9</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>-131.16</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="Z11" s="5" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AA11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF11" s="5" t="inlineStr">
+        <is>
+          <t>0/5</t>
+        </is>
+      </c>
+      <c r="AG11" s="5" t="n">
+        <v>16.9844</v>
+      </c>
+      <c r="AH11" s="5" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="AI11" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AJ11" s="5" t="n">
+        <v>56600577</v>
+      </c>
+      <c r="AK11" s="5" t="n">
+        <v>55223005</v>
+      </c>
+      <c r="AL11" s="5" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="AM11" s="5" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AN11" s="5" t="inlineStr">
+        <is>
+          <t>Fiyat 27-08-26 tarihinde yükselen destek (17-04-26–13-08-26, ~%2.5 yükseliş, 3 temas) çizgisini aşağı kırdı. OBV düşüşte; doğruluyor.</t>
+        </is>
+      </c>
       <c r="AO11" s="5" t="inlineStr"/>
-      <c r="AP11" s="5" t="inlineStr"/>
+      <c r="AP11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 11-08-26</t>
+        </is>
+      </c>
       <c r="AQ11" s="5" t="inlineStr"/>
-      <c r="AR11" s="5" t="inlineStr"/>
+      <c r="AR11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 12-08-26</t>
+        </is>
+      </c>
       <c r="AS11" s="5" t="inlineStr"/>
-      <c r="AT11" s="5" t="inlineStr"/>
+      <c r="AT11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 13-08-26</t>
+        </is>
+      </c>
       <c r="AU11" s="5" t="inlineStr"/>
-      <c r="AV11" s="5" t="inlineStr"/>
+      <c r="AV11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 17-08-26</t>
+        </is>
+      </c>
       <c r="AW11" s="5" t="inlineStr"/>
-      <c r="AX11" s="5" t="inlineStr"/>
+      <c r="AX11" s="7" t="inlineStr">
+        <is>
+          <t>▼ 24-08-26</t>
+        </is>
+      </c>
       <c r="AY11" s="5" t="inlineStr"/>
       <c r="AZ11" s="5" t="inlineStr"/>
       <c r="BA11" s="5" t="inlineStr"/>
@@ -6697,42 +7540,99 @@
       <c r="BD11" s="5" t="inlineStr"/>
       <c r="BE11" s="5" t="inlineStr"/>
       <c r="BF11" s="5" t="inlineStr"/>
-      <c r="BG11" s="5" t="inlineStr"/>
-      <c r="BH11" s="5" t="inlineStr"/>
-      <c r="BI11" s="5" t="inlineStr"/>
-      <c r="BJ11" s="5" t="inlineStr"/>
-      <c r="BK11" s="5" t="inlineStr"/>
-      <c r="BL11" s="5" t="inlineStr"/>
-      <c r="BM11" s="5" t="inlineStr"/>
-      <c r="BN11" s="5" t="inlineStr"/>
-      <c r="BO11" s="5" t="inlineStr"/>
-      <c r="BP11" s="5" t="inlineStr"/>
-      <c r="BQ11" s="5" t="inlineStr"/>
-      <c r="BR11" s="5" t="inlineStr"/>
-      <c r="BS11" s="5" t="inlineStr"/>
-      <c r="BT11" s="5" t="inlineStr"/>
-      <c r="BU11" s="5" t="inlineStr"/>
-      <c r="BV11" s="5" t="inlineStr"/>
-      <c r="BW11" s="5" t="inlineStr"/>
-      <c r="BX11" s="5" t="inlineStr"/>
-      <c r="BY11" s="5" t="inlineStr"/>
-      <c r="BZ11" s="5" t="inlineStr"/>
-      <c r="CA11" s="5" t="inlineStr"/>
-      <c r="CB11" s="5" t="inlineStr"/>
-      <c r="CC11" s="5" t="inlineStr"/>
-      <c r="CD11" s="5" t="inlineStr"/>
-      <c r="CE11" s="5" t="inlineStr"/>
-      <c r="CF11" s="5" t="inlineStr"/>
-      <c r="CG11" s="5" t="inlineStr"/>
+      <c r="BG11" s="5" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="BH11" s="5" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="BI11" s="5" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="BJ11" s="5" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="BK11" s="5" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="BL11" s="5" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="BM11" s="5" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="BN11" s="5" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="BO11" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BP11" s="5" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="BQ11" s="5" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="BR11" s="5" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="BS11" s="5" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="BT11" s="5" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="BU11" s="5" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="BV11" s="5" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="BW11" s="5" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="BX11" s="5" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="BY11" s="5" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="BZ11" s="5" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="CA11" s="5" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="CB11" s="7" t="inlineStr">
+        <is>
+          <t>▼</t>
+        </is>
+      </c>
+      <c r="CC11" s="5" t="inlineStr">
+        <is>
+          <t>T28 19-08-26 @19.61</t>
+        </is>
+      </c>
+      <c r="CD11" s="5" t="inlineStr">
+        <is>
+          <t>D31 13-08-26 @18.74</t>
+        </is>
+      </c>
+      <c r="CE11" s="5" t="inlineStr">
+        <is>
+          <t>27-08-26</t>
+        </is>
+      </c>
+      <c r="CF11" s="5" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="CG11" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="CH11" s="5" t="inlineStr"/>
-      <c r="CI11" s="5" t="inlineStr">
-        <is>
-          <t>KeyError: 'kind'</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CI11"/>
+  <autoFilter ref="A1:CH11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>